--- a/results/MM-urban5.xlsx
+++ b/results/MM-urban5.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alessiosclafani/Desktop/PhD/crawford/results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D678115F-A9B6-314C-92F8-33968D59A555}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD718EF0-C6E3-014B-A64E-6B66354BA723}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="820" yWindow="760" windowWidth="28040" windowHeight="17060" activeTab="2" xr2:uid="{8B2D79CE-CA72-194E-B6B8-B7E9664FC062}"/>
   </bookViews>
@@ -38,169 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="336">
-  <si>
-    <t>F_10;F_16;F_18;F_19;F_3;F_4;F_9</t>
-  </si>
-  <si>
-    <t>HUB_1;HUB_2</t>
-  </si>
-  <si>
-    <t>F_10;F_18;F_19;F_9</t>
-  </si>
-  <si>
-    <t>HUB_1;HUB_3</t>
-  </si>
-  <si>
-    <t>F_19;F_24;F_26</t>
-  </si>
-  <si>
-    <t>HUB_1</t>
-  </si>
-  <si>
-    <t>F_10;F_19</t>
-  </si>
-  <si>
-    <t>F_10;F_11;F_16;F_19;F_24;F_26</t>
-  </si>
-  <si>
-    <t>F_16;F_23;F_25</t>
-  </si>
-  <si>
-    <t>F_18;F_26;F_33</t>
-  </si>
-  <si>
-    <t>F_10;F_19;F_24;F_26;F_33</t>
-  </si>
-  <si>
-    <t>F_1;F_10;F_11;F_17;F_19;F_20</t>
-  </si>
-  <si>
-    <t>HUB_2;HUB_3</t>
-  </si>
-  <si>
-    <t>F_10;F_24;F_25;F_9</t>
-  </si>
-  <si>
-    <t>F_16;F_18;F_19;F_24;F_9</t>
-  </si>
-  <si>
-    <t>F_10;F_15;F_16;F_19;F_23;F_25;F_26;F_8</t>
-  </si>
-  <si>
-    <t>F_10;F_17;F_18;F_19;F_23;F_24;F_25;F_26</t>
-  </si>
-  <si>
-    <t>F_10;F_11;F_19;F_24;F_26;F_9</t>
-  </si>
-  <si>
-    <t>F_10;F_12;F_13;F_17;F_18;F_19;F_20;F_23;F_24;F_25;F_26;F_32;F_33;F_5;F_6</t>
-  </si>
-  <si>
-    <t>F_10;F_12;F_16;F_18;F_19;F_24;F_26;F_9</t>
-  </si>
-  <si>
-    <t>F_10;F_12;F_17;F_18;F_19;F_25;F_26</t>
-  </si>
-  <si>
-    <t>F_10;F_17;F_19;F_31</t>
-  </si>
-  <si>
-    <t>F_16;F_17;F_18;F_20;F_24</t>
-  </si>
-  <si>
-    <t>F_10;F_16;F_19;F_23;F_26;F_9</t>
-  </si>
-  <si>
-    <t>F_10;F_16;F_18;F_19;F_23;F_24;F_25;F_3;F_4;F_9</t>
-  </si>
-  <si>
-    <t>F_10;F_13;F_16;F_17;F_19;F_20;F_24;F_26;F_31</t>
-  </si>
-  <si>
-    <t>F_10;F_11;F_12;F_15;F_17;F_18;F_19;F_20;F_24;F_25;F_26;F_33;F_9</t>
-  </si>
-  <si>
-    <t>F_10;F_16;F_17;F_18;F_19;F_20;F_24;F_26;F_9</t>
-  </si>
-  <si>
-    <t>F_10;F_11;F_12;F_13;F_16;F_17;F_18;F_19;F_20;F_24;F_25;F_26;F_27;F_8;F_9</t>
-  </si>
-  <si>
-    <t>F_10;F_16;F_18;F_19;F_33;F_9</t>
-  </si>
-  <si>
-    <t>F_1;F_10;F_16;F_19;F_24;F_25;F_9</t>
-  </si>
-  <si>
-    <t>F_10;F_12;F_13;F_18;F_20;F_23;F_24;F_25;F_26;F_31</t>
-  </si>
-  <si>
-    <t>F_1;F_10;F_11;F_16;F_18;F_24;F_25;F_26;F_4;F_5</t>
-  </si>
-  <si>
-    <t>F_10;F_12;F_16;F_17;F_19;F_20;F_23;F_24;F_33;F_9</t>
-  </si>
-  <si>
-    <t>F_10;F_11;F_12;F_16;F_19;F_20;F_23;F_24;F_25;F_26;F_31;F_33;F_9</t>
-  </si>
-  <si>
-    <t>F_1;F_10;F_11;F_16;F_17;F_18;F_19;F_23;F_24;F_25;F_26;F_33</t>
-  </si>
-  <si>
-    <t>F_1;F_10;F_11;F_13;F_16;F_17;F_18;F_19;F_23;F_24;F_31</t>
-  </si>
-  <si>
-    <t>F_10;F_17;F_18;F_19;F_20;F_23;F_24;F_26</t>
-  </si>
-  <si>
-    <t>F_11;F_12;F_15;F_16;F_18;F_19;F_20;F_23;F_24;F_25;F_26;F_3;F_4;F_9</t>
-  </si>
-  <si>
-    <t>F_1;F_10;F_11;F_12;F_16;F_18;F_19;F_24;F_25;F_33;F_9</t>
-  </si>
-  <si>
-    <t>F_1;F_10;F_13;F_16;F_17;F_18;F_19;F_24;F_25;F_9</t>
-  </si>
-  <si>
-    <t>F_10;F_11;F_12;F_13;F_16;F_18;F_19;F_23;F_24;F_25;F_26;F_29;F_3;F_32;F_33;F_34;F_5;F_9</t>
-  </si>
-  <si>
-    <t>F_10;F_13;F_17;F_18;F_19;F_20;F_23;F_24;F_25;F_26;F_33</t>
-  </si>
-  <si>
-    <t>F_10;F_12;F_15;F_16;F_17;F_18;F_19;F_24;F_26;F_33;F_9</t>
-  </si>
-  <si>
-    <t>F_10;F_15;F_17;F_18;F_20;F_23;F_24;F_25;F_9</t>
-  </si>
-  <si>
-    <t>F_1;F_10;F_11;F_16;F_17;F_18;F_19;F_24;F_25;F_26</t>
-  </si>
-  <si>
-    <t>F_1;F_10;F_12;F_16;F_17;F_19;F_20;F_25;F_26;F_33;F_9</t>
-  </si>
-  <si>
-    <t>F_1;F_10;F_13;F_16;F_17;F_19;F_24;F_25;F_26;F_33;F_9</t>
-  </si>
-  <si>
-    <t>F_10;F_11;F_12;F_14;F_16;F_17;F_18;F_19;F_20;F_21;F_23;F_24;F_25;F_26;F_27;F_33;F_6;F_9</t>
-  </si>
-  <si>
-    <t>F_10;F_16;F_18;F_20;F_23;F_24;F_25;F_33</t>
-  </si>
-  <si>
-    <t>F_10;F_11;F_12;F_16;F_17;F_18;F_19;F_20;F_24;F_25;F_26;F_3;F_4;F_9</t>
-  </si>
-  <si>
-    <t>F_10;F_11;F_16;F_17;F_18;F_19;F_20;F_24;F_25;F_26;F_31;F_32;F_33;F_9</t>
-  </si>
-  <si>
-    <t>F_1;F_10;F_16;F_17;F_18;F_19;F_23;F_24;F_25;F_9</t>
-  </si>
-  <si>
-    <t>F_1;F_10;F_15;F_16;F_18;F_19;F_22;F_23;F_24;F_25;F_26;F_3;F_31;F_33;F_4;F_9</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="181">
   <si>
     <t>N.H. o-d</t>
   </si>
@@ -286,12 +124,6 @@
     <t>N. HUBS ARCS</t>
   </si>
   <si>
-    <t>ACTIVE_FACILITIES</t>
-  </si>
-  <si>
-    <t>ACTIVE_HUBS</t>
-  </si>
-  <si>
     <t>Model Build Time</t>
   </si>
   <si>
@@ -299,303 +131,6 @@
   </si>
   <si>
     <t>TIME(s)</t>
-  </si>
-  <si>
-    <t>F_10;F_13;F_14;F_15;F_18;F_19;F_2;F_20;F_24;F_25;F_27;F_3;F_4;F_8;F_9</t>
-  </si>
-  <si>
-    <t>F_14;F_3;F_9</t>
-  </si>
-  <si>
-    <t>F_15;F_20</t>
-  </si>
-  <si>
-    <t>F_14;F_15;F_7</t>
-  </si>
-  <si>
-    <t>F_19;F_3;F_8</t>
-  </si>
-  <si>
-    <t>F_14;F_19;F_3;F_7;F_9</t>
-  </si>
-  <si>
-    <t>F_13;F_14;F_15;F_7</t>
-  </si>
-  <si>
-    <t>F_14;F_15;F_19;F_9</t>
-  </si>
-  <si>
-    <t>F_14;F_19;F_9</t>
-  </si>
-  <si>
-    <t>F_14;F_23;F_24;F_25;F_9</t>
-  </si>
-  <si>
-    <t>F_13;F_14;F_19;F_3</t>
-  </si>
-  <si>
-    <t>F_11;F_12;F_13;F_14;F_15;F_17;F_18;F_19;F_3;F_4;F_6;F_7;F_8;F_9</t>
-  </si>
-  <si>
-    <t>F_13;F_14;F_15;F_18;F_19;F_20;F_23;F_24;F_25;F_3;F_4;F_5;F_8;F_9</t>
-  </si>
-  <si>
-    <t>F_13;F_15;F_19;F_2;F_20;F_24;F_8</t>
-  </si>
-  <si>
-    <t>F_12;F_14;F_15;F_17;F_18;F_19;F_4;F_5;F_7;F_8</t>
-  </si>
-  <si>
-    <t>F_13;F_14;F_15;F_19;F_7</t>
-  </si>
-  <si>
-    <t>F_14;F_15;F_19;F_20;F_3;F_9</t>
-  </si>
-  <si>
-    <t>F_13;F_14;F_15;F_19;F_7;F_8</t>
-  </si>
-  <si>
-    <t>F_13;F_14;F_15;F_20;F_4;F_7;F_8;F_9</t>
-  </si>
-  <si>
-    <t>F_13;F_14;F_15;F_18;F_19;F_20;F_24;F_25;F_3;F_8;F_9</t>
-  </si>
-  <si>
-    <t>F_13;F_14;F_15;F_19;F_2;F_3;F_4;F_8</t>
-  </si>
-  <si>
-    <t>F_10;F_13;F_14;F_15;F_19;F_20</t>
-  </si>
-  <si>
-    <t>F_13;F_14;F_15;F_18;F_19;F_20;F_8;F_9</t>
-  </si>
-  <si>
-    <t>F_12;F_13;F_14;F_15;F_18;F_19;F_3;F_4;F_5;F_7;F_8;F_9</t>
-  </si>
-  <si>
-    <t>F_12;F_13;F_14;F_15;F_18;F_19;F_3;F_8;F_9</t>
-  </si>
-  <si>
-    <t>F_14;F_20</t>
-  </si>
-  <si>
-    <t>F_14;F_19;F_4;F_8;F_9</t>
-  </si>
-  <si>
-    <t>F_14;F_15;F_18;F_19;F_2;F_20;F_3;F_8;F_9</t>
-  </si>
-  <si>
-    <t>F_10;F_12;F_13;F_14;F_15;F_18;F_19;F_3;F_8</t>
-  </si>
-  <si>
-    <t>F_14;F_15;F_19;F_24;F_8;F_9</t>
-  </si>
-  <si>
-    <t>F_1;F_12;F_13;F_14;F_15;F_18;F_19;F_2;F_20;F_25;F_3;F_4;F_7;F_8;F_9</t>
-  </si>
-  <si>
-    <t>F_13;F_14;F_15;F_19;F_4;F_8;F_9</t>
-  </si>
-  <si>
-    <t>F_13;F_14;F_15;F_19;F_20;F_24;F_4;F_8</t>
-  </si>
-  <si>
-    <t>F_10;F_13;F_14;F_15;F_19;F_20;F_8;F_9</t>
-  </si>
-  <si>
-    <t>F_13;F_14;F_15;F_19;F_20;F_3</t>
-  </si>
-  <si>
-    <t>F_10;F_13;F_14;F_19;F_7;F_8;F_9</t>
-  </si>
-  <si>
-    <t>F_12;F_13;F_14;F_19;F_7;F_8</t>
-  </si>
-  <si>
-    <t>F_10;F_13;F_14;F_15;F_18;F_19;F_24;F_3;F_9</t>
-  </si>
-  <si>
-    <t>F_14;F_19;F_7;F_9</t>
-  </si>
-  <si>
-    <t>F_14;F_15;F_19;F_20;F_3;F_4;F_9</t>
-  </si>
-  <si>
-    <t>F_13;F_14;F_15;F_19;F_20;F_3;F_7;F_8;F_9</t>
-  </si>
-  <si>
-    <t>F_14;F_15;F_19;F_20;F_7;F_8</t>
-  </si>
-  <si>
-    <t>F_10;F_12;F_13;F_14;F_15;F_18;F_19;F_2;F_20;F_3;F_30;F_6;F_7;F_8;F_9</t>
-  </si>
-  <si>
-    <t>F_13;F_14;F_15;F_19;F_3;F_7</t>
-  </si>
-  <si>
-    <t>F_14;F_15;F_19;F_2;F_20;F_7;F_8</t>
-  </si>
-  <si>
-    <t>F_10;F_14;F_15;F_19;F_2;F_20;F_3;F_4;F_7;F_8</t>
-  </si>
-  <si>
-    <t>F_10;F_13;F_14;F_15;F_18;F_19;F_20;F_25;F_3;F_7</t>
-  </si>
-  <si>
-    <t>F_10;F_13;F_14;F_15;F_19;F_3;F_7</t>
-  </si>
-  <si>
-    <t>F_12;F_13;F_14;F_15;F_18;F_19;F_20;F_24;F_3;F_4;F_8</t>
-  </si>
-  <si>
-    <t>F_10;F_13;F_14;F_15;F_19;F_20;F_3;F_4;F_7;F_8;F_9</t>
-  </si>
-  <si>
-    <t>F_11;F_17;F_19;F_26;F_9</t>
-  </si>
-  <si>
-    <t>F_17;F_18;F_2;F_4</t>
-  </si>
-  <si>
-    <t>F_16;F_19;F_24</t>
-  </si>
-  <si>
-    <t>F_11</t>
-  </si>
-  <si>
-    <t>F_11;F_16;F_24;F_26;F_9</t>
-  </si>
-  <si>
-    <t>F_17;F_26</t>
-  </si>
-  <si>
-    <t>F_17;F_18;F_26;F_9</t>
-  </si>
-  <si>
-    <t>F_17;F_25</t>
-  </si>
-  <si>
-    <t>F_17;F_24</t>
-  </si>
-  <si>
-    <t>F_17;F_18;F_26</t>
-  </si>
-  <si>
-    <t>F_16;F_18;F_19;F_24;F_25;F_31;F_8;F_9</t>
-  </si>
-  <si>
-    <t>F_1;F_10;F_11;F_12;F_16;F_17;F_18;F_19;F_2;F_20;F_23;F_24;F_25;F_26;F_27;F_32;F_4;F_8;F_9</t>
-  </si>
-  <si>
-    <t>F_10;F_11;F_16;F_17;F_18;F_25;F_26;F_9</t>
-  </si>
-  <si>
-    <t>F_16;F_17;F_18;F_2;F_4;F_8;F_9</t>
-  </si>
-  <si>
-    <t>F_11;F_17;F_18;F_19;F_24;F_25;F_26;F_9</t>
-  </si>
-  <si>
-    <t>F_11;F_12;F_15;F_16;F_19;F_2;F_20;F_21;F_25;F_27;F_31;F_32;F_33;F_39;F_4;F_40;F_8;F_9</t>
-  </si>
-  <si>
-    <t>F_11;F_16;F_17;F_18;F_24;F_26;F_31</t>
-  </si>
-  <si>
-    <t>F_1;F_10;F_12;F_15;F_16;F_17;F_18;F_19;F_2;F_23;F_24;F_25;F_26;F_31;F_8;F_9</t>
-  </si>
-  <si>
-    <t>F_11;F_16;F_17;F_18;F_19;F_24;F_25;F_9</t>
-  </si>
-  <si>
-    <t>F_11;F_16;F_17;F_18;F_19;F_24;F_25;F_8;F_9</t>
-  </si>
-  <si>
-    <t>F_16;F_17;F_18;F_19;F_2;F_24;F_25;F_26;F_31;F_32;F_33;F_4</t>
-  </si>
-  <si>
-    <t>F_12;F_16;F_17;F_2;F_23;F_4;F_9</t>
-  </si>
-  <si>
-    <t>F_11;F_12;F_15;F_16;F_17;F_18;F_2;F_24;F_25;F_26;F_4;F_8</t>
-  </si>
-  <si>
-    <t>F_17;F_18;F_2;F_23;F_24;F_26;F_31;F_4;F_9</t>
-  </si>
-  <si>
-    <t>F_11;F_17;F_19;F_23;F_25;F_32;F_9</t>
-  </si>
-  <si>
-    <t>F_10;F_11;F_16;F_17;F_18;F_19;F_24;F_25;F_26;F_9</t>
-  </si>
-  <si>
-    <t>F_11;F_16;F_17;F_18;F_19;F_23;F_24;F_25;F_26;F_9</t>
-  </si>
-  <si>
-    <t>F_10;F_11;F_16;F_17;F_18;F_19;F_24;F_26;F_31;F_9</t>
-  </si>
-  <si>
-    <t>F_11;F_12;F_16;F_17;F_24;F_25;F_9</t>
-  </si>
-  <si>
-    <t>F_10;F_11;F_15;F_17;F_18;F_19;F_23;F_24;F_25;F_26;F_31;F_32;F_33;F_35;F_8;F_9</t>
-  </si>
-  <si>
-    <t>F_11;F_16;F_17;F_18;F_19;F_2;F_23;F_24;F_25;F_4;F_8;F_9</t>
-  </si>
-  <si>
-    <t>F_11;F_12;F_16;F_17;F_18;F_19;F_24;F_25;F_26;F_9</t>
-  </si>
-  <si>
-    <t>F_11;F_16;F_17;F_18;F_19;F_25;F_26;F_8;F_9</t>
-  </si>
-  <si>
-    <t>F_10;F_11;F_16;F_17;F_18;F_19;F_25;F_26;F_31;F_8</t>
-  </si>
-  <si>
-    <t>F_10;F_11;F_16;F_17;F_18;F_23;F_24;F_25;F_31;F_9</t>
-  </si>
-  <si>
-    <t>F_11;F_16;F_17;F_18;F_24;F_32;F_9</t>
-  </si>
-  <si>
-    <t>F_10;F_11;F_12;F_13;F_15;F_16;F_17;F_18;F_19;F_2;F_23;F_24;F_25;F_3;F_30;F_31;F_32;F_8;F_9</t>
-  </si>
-  <si>
-    <t>F_11;F_12;F_16;F_17;F_18;F_19;F_24;F_25;F_26;F_31;F_32</t>
-  </si>
-  <si>
-    <t>F_11;F_15;F_16;F_17;F_18;F_2;F_23;F_24;F_25;F_26;F_4;F_9</t>
-  </si>
-  <si>
-    <t>F_10;F_11;F_16;F_17;F_18;F_19;F_23;F_24;F_25;F_32;F_9</t>
-  </si>
-  <si>
-    <t>F_11;F_16;F_17;F_18;F_2;F_24;F_25;F_26;F_31;F_4;F_9</t>
-  </si>
-  <si>
-    <t>F_10;F_11;F_15;F_16;F_17;F_18;F_19;F_25;F_26;F_32;F_8;F_9</t>
-  </si>
-  <si>
-    <t>F_11;F_16;F_17;F_18;F_23;F_24;F_25;F_26;F_32;F_8;F_9</t>
-  </si>
-  <si>
-    <t>F_10;F_11;F_12;F_16;F_17;F_18;F_23;F_24;F_25;F_31;F_32;F_8;F_9</t>
-  </si>
-  <si>
-    <t>F_10;F_16;F_17;F_18;F_19;F_25;F_26;F_8;F_9</t>
-  </si>
-  <si>
-    <t>F_10;F_11;F_16;F_17;F_18;F_19;F_23;F_24;F_25;F_9</t>
-  </si>
-  <si>
-    <t>F_11;F_16;F_17;F_18;F_19;F_25;F_31;F_9</t>
-  </si>
-  <si>
-    <t>F_10;F_16;F_17;F_18;F_19;F_23;F_24;F_26;F_8;F_9</t>
-  </si>
-  <si>
-    <t>F_10;F_11;F_12;F_16;F_17;F_18;F_19;F_2;F_23;F_24;F_25;F_26;F_4;F_8;F_9</t>
   </si>
   <si>
     <t>ROMA-10-1-c</t>
@@ -1418,113 +953,107 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8ED1B722-279D-2743-A951-F1061F019B44}">
-  <dimension ref="A1:AH51"/>
+  <dimension ref="A1:AF51"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B1" t="s">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>55</v>
+        <v>1</v>
       </c>
       <c r="D1" t="s">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="E1" t="s">
-        <v>57</v>
+        <v>3</v>
       </c>
       <c r="F1" t="s">
-        <v>58</v>
+        <v>4</v>
       </c>
       <c r="G1" t="s">
-        <v>59</v>
+        <v>5</v>
       </c>
       <c r="H1" t="s">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="I1" t="s">
-        <v>61</v>
+        <v>7</v>
       </c>
       <c r="J1" t="s">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="K1" t="s">
-        <v>63</v>
+        <v>9</v>
       </c>
       <c r="L1" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
       <c r="M1" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="N1" t="s">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="O1" t="s">
-        <v>67</v>
+        <v>13</v>
       </c>
       <c r="P1" t="s">
-        <v>68</v>
+        <v>14</v>
       </c>
       <c r="Q1" t="s">
-        <v>69</v>
+        <v>15</v>
       </c>
       <c r="R1" t="s">
-        <v>70</v>
+        <v>16</v>
       </c>
       <c r="S1" t="s">
-        <v>71</v>
+        <v>17</v>
       </c>
       <c r="T1" t="s">
-        <v>72</v>
+        <v>18</v>
       </c>
       <c r="U1" t="s">
-        <v>73</v>
+        <v>19</v>
       </c>
       <c r="V1" t="s">
-        <v>74</v>
+        <v>20</v>
       </c>
       <c r="W1" t="s">
-        <v>75</v>
+        <v>21</v>
       </c>
       <c r="X1" t="s">
-        <v>76</v>
+        <v>22</v>
       </c>
       <c r="Y1" t="s">
-        <v>77</v>
+        <v>23</v>
       </c>
       <c r="Z1" t="s">
-        <v>78</v>
+        <v>24</v>
       </c>
       <c r="AA1" t="s">
-        <v>79</v>
+        <v>25</v>
       </c>
       <c r="AB1" t="s">
-        <v>80</v>
+        <v>26</v>
       </c>
       <c r="AC1" t="s">
-        <v>81</v>
+        <v>27</v>
       </c>
       <c r="AD1" t="s">
-        <v>82</v>
+        <v>28</v>
       </c>
       <c r="AE1" t="s">
-        <v>83</v>
+        <v>29</v>
       </c>
       <c r="AF1" t="s">
-        <v>84</v>
-      </c>
-      <c r="AG1" t="s">
-        <v>85</v>
-      </c>
-      <c r="AH1" t="s">
-        <v>86</v>
+        <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>186</v>
+        <v>31</v>
       </c>
       <c r="B2">
         <v>10</v>
@@ -1611,25 +1140,19 @@
       <c r="AC2">
         <v>10</v>
       </c>
-      <c r="AD2" t="s">
-        <v>137</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>1</v>
+      <c r="AD2">
+        <v>13.5188107490539</v>
+      </c>
+      <c r="AE2">
+        <v>7.70804715156555</v>
       </c>
       <c r="AF2">
-        <v>13.5188107490539</v>
-      </c>
-      <c r="AG2">
-        <v>7.70804715156555</v>
-      </c>
-      <c r="AH2">
         <v>21.2268579006195</v>
       </c>
     </row>
-    <row r="3" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>187</v>
+        <v>32</v>
       </c>
       <c r="B3">
         <v>10</v>
@@ -1716,25 +1239,19 @@
       <c r="AC3">
         <v>8</v>
       </c>
-      <c r="AD3" t="s">
-        <v>138</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>3</v>
+      <c r="AD3">
+        <v>13.816669940948399</v>
+      </c>
+      <c r="AE3">
+        <v>7.3848459720611501</v>
       </c>
       <c r="AF3">
-        <v>13.816669940948399</v>
-      </c>
-      <c r="AG3">
-        <v>7.3848459720611501</v>
-      </c>
-      <c r="AH3">
         <v>21.201515913009601</v>
       </c>
     </row>
-    <row r="4" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>188</v>
+        <v>33</v>
       </c>
       <c r="B4">
         <v>10</v>
@@ -1821,25 +1338,19 @@
       <c r="AC4">
         <v>8</v>
       </c>
-      <c r="AD4" t="s">
-        <v>139</v>
-      </c>
-      <c r="AE4" t="s">
-        <v>1</v>
+      <c r="AD4">
+        <v>13.6108078956604</v>
+      </c>
+      <c r="AE4">
+        <v>5.34980988502502</v>
       </c>
       <c r="AF4">
-        <v>13.6108078956604</v>
-      </c>
-      <c r="AG4">
-        <v>5.34980988502502</v>
-      </c>
-      <c r="AH4">
         <v>18.9606177806854</v>
       </c>
     </row>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>189</v>
+        <v>34</v>
       </c>
       <c r="B5">
         <v>10</v>
@@ -1926,25 +1437,19 @@
       <c r="AC5">
         <v>7</v>
       </c>
-      <c r="AD5" t="s">
-        <v>140</v>
-      </c>
-      <c r="AE5" t="s">
-        <v>5</v>
+      <c r="AD5">
+        <v>13.4117631912231</v>
+      </c>
+      <c r="AE5">
+        <v>5.1563332080841002</v>
       </c>
       <c r="AF5">
-        <v>13.4117631912231</v>
-      </c>
-      <c r="AG5">
-        <v>5.1563332080841002</v>
-      </c>
-      <c r="AH5">
         <v>18.568096399307201</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>190</v>
+        <v>35</v>
       </c>
       <c r="B6">
         <v>10</v>
@@ -2031,25 +1536,19 @@
       <c r="AC6">
         <v>8</v>
       </c>
-      <c r="AD6" t="s">
-        <v>141</v>
-      </c>
-      <c r="AE6" t="s">
-        <v>3</v>
+      <c r="AD6">
+        <v>12.981688022613501</v>
+      </c>
+      <c r="AE6">
+        <v>4.8102681636810303</v>
       </c>
       <c r="AF6">
-        <v>12.981688022613501</v>
-      </c>
-      <c r="AG6">
-        <v>4.8102681636810303</v>
-      </c>
-      <c r="AH6">
         <v>17.791956186294499</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>191</v>
+        <v>36</v>
       </c>
       <c r="B7">
         <v>10</v>
@@ -2136,25 +1635,19 @@
       <c r="AC7">
         <v>9</v>
       </c>
-      <c r="AD7" t="s">
-        <v>142</v>
-      </c>
-      <c r="AE7" t="s">
-        <v>1</v>
+      <c r="AD7">
+        <v>13.847862005233701</v>
+      </c>
+      <c r="AE7">
+        <v>5.1342201232910103</v>
       </c>
       <c r="AF7">
-        <v>13.847862005233701</v>
-      </c>
-      <c r="AG7">
-        <v>5.1342201232910103</v>
-      </c>
-      <c r="AH7">
         <v>18.982082128524699</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>192</v>
+        <v>37</v>
       </c>
       <c r="B8">
         <v>10</v>
@@ -2241,25 +1734,19 @@
       <c r="AC8">
         <v>6</v>
       </c>
-      <c r="AD8" t="s">
-        <v>143</v>
-      </c>
-      <c r="AE8" t="s">
-        <v>1</v>
+      <c r="AD8">
+        <v>12.7589478492736</v>
+      </c>
+      <c r="AE8">
+        <v>4.99877500534057</v>
       </c>
       <c r="AF8">
-        <v>12.7589478492736</v>
-      </c>
-      <c r="AG8">
-        <v>4.99877500534057</v>
-      </c>
-      <c r="AH8">
         <v>17.757722854614201</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>193</v>
+        <v>38</v>
       </c>
       <c r="B9">
         <v>10</v>
@@ -2346,25 +1833,19 @@
       <c r="AC9">
         <v>6</v>
       </c>
-      <c r="AD9" t="s">
-        <v>144</v>
-      </c>
-      <c r="AE9" t="s">
-        <v>5</v>
+      <c r="AD9">
+        <v>14.697014093399</v>
+      </c>
+      <c r="AE9">
+        <v>5.4310610294341997</v>
       </c>
       <c r="AF9">
-        <v>14.697014093399</v>
-      </c>
-      <c r="AG9">
-        <v>5.4310610294341997</v>
-      </c>
-      <c r="AH9">
         <v>20.128075122833199</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>194</v>
+        <v>39</v>
       </c>
       <c r="B10">
         <v>10</v>
@@ -2451,25 +1932,19 @@
       <c r="AC10">
         <v>4</v>
       </c>
-      <c r="AD10" t="s">
-        <v>145</v>
-      </c>
-      <c r="AE10" t="s">
-        <v>3</v>
+      <c r="AD10">
+        <v>13.484207868576</v>
+      </c>
+      <c r="AE10">
+        <v>4.7996022701263401</v>
       </c>
       <c r="AF10">
-        <v>13.484207868576</v>
-      </c>
-      <c r="AG10">
-        <v>4.7996022701263401</v>
-      </c>
-      <c r="AH10">
         <v>18.2838101387023</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>195</v>
+        <v>40</v>
       </c>
       <c r="B11">
         <v>10</v>
@@ -2556,25 +2031,19 @@
       <c r="AC11">
         <v>8</v>
       </c>
-      <c r="AD11" t="s">
-        <v>145</v>
-      </c>
-      <c r="AE11" t="s">
-        <v>1</v>
+      <c r="AD11">
+        <v>14.0187129974365</v>
+      </c>
+      <c r="AE11">
+        <v>5.1986200809478698</v>
       </c>
       <c r="AF11">
-        <v>14.0187129974365</v>
-      </c>
-      <c r="AG11">
-        <v>5.1986200809478698</v>
-      </c>
-      <c r="AH11">
         <v>19.217333078384399</v>
       </c>
     </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>196</v>
+        <v>41</v>
       </c>
       <c r="B12">
         <v>20</v>
@@ -2661,25 +2130,19 @@
       <c r="AC12">
         <v>12</v>
       </c>
-      <c r="AD12" t="s">
-        <v>146</v>
-      </c>
-      <c r="AE12" t="s">
-        <v>1</v>
+      <c r="AD12">
+        <v>57.525588989257798</v>
+      </c>
+      <c r="AE12">
+        <v>19.768794775009098</v>
       </c>
       <c r="AF12">
-        <v>57.525588989257798</v>
-      </c>
-      <c r="AG12">
-        <v>19.768794775009098</v>
-      </c>
-      <c r="AH12">
         <v>77.294383764266897</v>
       </c>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>197</v>
+        <v>42</v>
       </c>
       <c r="B13">
         <v>20</v>
@@ -2766,25 +2229,19 @@
       <c r="AC13">
         <v>6</v>
       </c>
-      <c r="AD13" t="s">
-        <v>147</v>
-      </c>
-      <c r="AE13" t="s">
-        <v>1</v>
+      <c r="AD13">
+        <v>53.047181844711297</v>
+      </c>
+      <c r="AE13">
+        <v>19.549874305725002</v>
       </c>
       <c r="AF13">
-        <v>53.047181844711297</v>
-      </c>
-      <c r="AG13">
-        <v>19.549874305725002</v>
-      </c>
-      <c r="AH13">
         <v>72.597056150436401</v>
       </c>
     </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>198</v>
+        <v>43</v>
       </c>
       <c r="B14">
         <v>20</v>
@@ -2871,25 +2328,19 @@
       <c r="AC14">
         <v>15</v>
       </c>
-      <c r="AD14" t="s">
-        <v>148</v>
-      </c>
-      <c r="AE14" t="s">
-        <v>1</v>
+      <c r="AD14">
+        <v>50.052428245544398</v>
+      </c>
+      <c r="AE14">
+        <v>64.172782659530597</v>
       </c>
       <c r="AF14">
-        <v>50.052428245544398</v>
-      </c>
-      <c r="AG14">
-        <v>64.172782659530597</v>
-      </c>
-      <c r="AH14">
         <v>114.225210905075</v>
       </c>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>199</v>
+        <v>44</v>
       </c>
       <c r="B15">
         <v>20</v>
@@ -2976,25 +2427,19 @@
       <c r="AC15">
         <v>8</v>
       </c>
-      <c r="AD15" t="s">
-        <v>149</v>
-      </c>
-      <c r="AE15" t="s">
-        <v>1</v>
+      <c r="AD15">
+        <v>54.250692844390798</v>
+      </c>
+      <c r="AE15">
+        <v>19.396953105926499</v>
       </c>
       <c r="AF15">
-        <v>54.250692844390798</v>
-      </c>
-      <c r="AG15">
-        <v>19.396953105926499</v>
-      </c>
-      <c r="AH15">
         <v>73.647645950317298</v>
       </c>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>200</v>
+        <v>45</v>
       </c>
       <c r="B16">
         <v>20</v>
@@ -3081,25 +2526,19 @@
       <c r="AC16">
         <v>17</v>
       </c>
-      <c r="AD16" t="s">
-        <v>150</v>
-      </c>
-      <c r="AE16" t="s">
-        <v>3</v>
+      <c r="AD16">
+        <v>51.644581079482997</v>
+      </c>
+      <c r="AE16">
+        <v>35.266108989715498</v>
       </c>
       <c r="AF16">
-        <v>51.644581079482997</v>
-      </c>
-      <c r="AG16">
-        <v>35.266108989715498</v>
-      </c>
-      <c r="AH16">
         <v>86.910690069198594</v>
       </c>
     </row>
-    <row r="17" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>201</v>
+        <v>46</v>
       </c>
       <c r="B17">
         <v>20</v>
@@ -3186,25 +2625,19 @@
       <c r="AC17">
         <v>14</v>
       </c>
-      <c r="AD17" t="s">
-        <v>151</v>
-      </c>
-      <c r="AE17" t="s">
-        <v>1</v>
+      <c r="AD17">
+        <v>54.105852842330897</v>
+      </c>
+      <c r="AE17">
+        <v>50.085645198822</v>
       </c>
       <c r="AF17">
-        <v>54.105852842330897</v>
-      </c>
-      <c r="AG17">
-        <v>50.085645198822</v>
-      </c>
-      <c r="AH17">
         <v>104.191498041152</v>
       </c>
     </row>
-    <row r="18" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>202</v>
+        <v>47</v>
       </c>
       <c r="B18">
         <v>20</v>
@@ -3291,25 +2724,19 @@
       <c r="AC18">
         <v>14</v>
       </c>
-      <c r="AD18" t="s">
-        <v>152</v>
-      </c>
-      <c r="AE18" t="s">
-        <v>1</v>
+      <c r="AD18">
+        <v>57.744593143463099</v>
+      </c>
+      <c r="AE18">
+        <v>40.1415917873382</v>
       </c>
       <c r="AF18">
-        <v>57.744593143463099</v>
-      </c>
-      <c r="AG18">
-        <v>40.1415917873382</v>
-      </c>
-      <c r="AH18">
         <v>97.886184930801306</v>
       </c>
     </row>
-    <row r="19" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>203</v>
+        <v>48</v>
       </c>
       <c r="B19">
         <v>20</v>
@@ -3396,25 +2823,19 @@
       <c r="AC19">
         <v>13</v>
       </c>
-      <c r="AD19" t="s">
-        <v>153</v>
-      </c>
-      <c r="AE19" t="s">
-        <v>12</v>
+      <c r="AD19">
+        <v>50.5706691741943</v>
+      </c>
+      <c r="AE19">
+        <v>54.267643928527797</v>
       </c>
       <c r="AF19">
-        <v>50.5706691741943</v>
-      </c>
-      <c r="AG19">
-        <v>54.267643928527797</v>
-      </c>
-      <c r="AH19">
         <v>104.838313102722</v>
       </c>
     </row>
-    <row r="20" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>204</v>
+        <v>49</v>
       </c>
       <c r="B20">
         <v>20</v>
@@ -3501,25 +2922,19 @@
       <c r="AC20">
         <v>12</v>
       </c>
-      <c r="AD20" t="s">
-        <v>154</v>
-      </c>
-      <c r="AE20" t="s">
-        <v>3</v>
+      <c r="AD20">
+        <v>51.789721250534001</v>
+      </c>
+      <c r="AE20">
+        <v>46.503871917724602</v>
       </c>
       <c r="AF20">
-        <v>51.789721250534001</v>
-      </c>
-      <c r="AG20">
-        <v>46.503871917724602</v>
-      </c>
-      <c r="AH20">
         <v>98.293593168258596</v>
       </c>
     </row>
-    <row r="21" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>205</v>
+        <v>50</v>
       </c>
       <c r="B21">
         <v>20</v>
@@ -3606,25 +3021,19 @@
       <c r="AC21">
         <v>7</v>
       </c>
-      <c r="AD21" t="s">
-        <v>155</v>
-      </c>
-      <c r="AE21" t="s">
-        <v>1</v>
+      <c r="AD21">
+        <v>53.025630950927699</v>
+      </c>
+      <c r="AE21">
+        <v>19.593659162521298</v>
       </c>
       <c r="AF21">
-        <v>53.025630950927699</v>
-      </c>
-      <c r="AG21">
-        <v>19.593659162521298</v>
-      </c>
-      <c r="AH21">
         <v>72.619290113449097</v>
       </c>
     </row>
-    <row r="22" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>206</v>
+        <v>51</v>
       </c>
       <c r="B22">
         <v>30</v>
@@ -3711,25 +3120,19 @@
       <c r="AC22">
         <v>21</v>
       </c>
-      <c r="AD22" t="s">
-        <v>156</v>
-      </c>
-      <c r="AE22" t="s">
-        <v>12</v>
+      <c r="AD22">
+        <v>166.10997486114499</v>
+      </c>
+      <c r="AE22">
+        <v>121.645008802413</v>
       </c>
       <c r="AF22">
-        <v>166.10997486114499</v>
-      </c>
-      <c r="AG22">
-        <v>121.645008802413</v>
-      </c>
-      <c r="AH22">
         <v>287.75498366355799</v>
       </c>
     </row>
-    <row r="23" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>207</v>
+        <v>52</v>
       </c>
       <c r="B23">
         <v>30</v>
@@ -3816,25 +3219,19 @@
       <c r="AC23">
         <v>27</v>
       </c>
-      <c r="AD23" t="s">
-        <v>157</v>
-      </c>
-      <c r="AE23" t="s">
-        <v>1</v>
+      <c r="AD23">
+        <v>128.314247846603</v>
+      </c>
+      <c r="AE23">
+        <v>78.065028190612793</v>
       </c>
       <c r="AF23">
-        <v>128.314247846603</v>
-      </c>
-      <c r="AG23">
-        <v>78.065028190612793</v>
-      </c>
-      <c r="AH23">
         <v>206.37927603721599</v>
       </c>
     </row>
-    <row r="24" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>208</v>
+        <v>53</v>
       </c>
       <c r="B24">
         <v>30</v>
@@ -3921,25 +3318,19 @@
       <c r="AC24">
         <v>5</v>
       </c>
-      <c r="AD24" t="s">
-        <v>158</v>
-      </c>
-      <c r="AE24" t="s">
-        <v>1</v>
+      <c r="AD24">
+        <v>144.72955298423699</v>
+      </c>
+      <c r="AE24">
+        <v>36.863820075988698</v>
       </c>
       <c r="AF24">
-        <v>144.72955298423699</v>
-      </c>
-      <c r="AG24">
-        <v>36.863820075988698</v>
-      </c>
-      <c r="AH24">
         <v>181.59337306022601</v>
       </c>
     </row>
-    <row r="25" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>209</v>
+        <v>54</v>
       </c>
       <c r="B25">
         <v>30</v>
@@ -4026,25 +3417,19 @@
       <c r="AC25">
         <v>12</v>
       </c>
-      <c r="AD25" t="s">
-        <v>159</v>
-      </c>
-      <c r="AE25" t="s">
-        <v>3</v>
+      <c r="AD25">
+        <v>134.670110940933</v>
+      </c>
+      <c r="AE25">
+        <v>67.231224060058594</v>
       </c>
       <c r="AF25">
-        <v>134.670110940933</v>
-      </c>
-      <c r="AG25">
-        <v>67.231224060058594</v>
-      </c>
-      <c r="AH25">
         <v>201.901335000991</v>
       </c>
     </row>
-    <row r="26" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>210</v>
+        <v>55</v>
       </c>
       <c r="B26">
         <v>30</v>
@@ -4131,25 +3516,19 @@
       <c r="AC26">
         <v>21</v>
       </c>
-      <c r="AD26" t="s">
-        <v>160</v>
-      </c>
-      <c r="AE26" t="s">
-        <v>1</v>
+      <c r="AD26">
+        <v>140.50807905197101</v>
+      </c>
+      <c r="AE26">
+        <v>45.387966871261597</v>
       </c>
       <c r="AF26">
-        <v>140.50807905197101</v>
-      </c>
-      <c r="AG26">
-        <v>45.387966871261597</v>
-      </c>
-      <c r="AH26">
         <v>185.896045923233</v>
       </c>
     </row>
-    <row r="27" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>211</v>
+        <v>56</v>
       </c>
       <c r="B27">
         <v>30</v>
@@ -4236,25 +3615,19 @@
       <c r="AC27">
         <v>28</v>
       </c>
-      <c r="AD27" t="s">
-        <v>161</v>
-      </c>
-      <c r="AE27" t="s">
-        <v>1</v>
+      <c r="AD27">
+        <v>142.90103077888401</v>
+      </c>
+      <c r="AE27">
+        <v>111.915778160095</v>
       </c>
       <c r="AF27">
-        <v>142.90103077888401</v>
-      </c>
-      <c r="AG27">
-        <v>111.915778160095</v>
-      </c>
-      <c r="AH27">
         <v>254.81680893897999</v>
       </c>
     </row>
-    <row r="28" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>212</v>
+        <v>57</v>
       </c>
       <c r="B28">
         <v>30</v>
@@ -4341,25 +3714,19 @@
       <c r="AC28">
         <v>12</v>
       </c>
-      <c r="AD28" t="s">
-        <v>162</v>
-      </c>
-      <c r="AE28" t="s">
-        <v>3</v>
+      <c r="AD28">
+        <v>138.64402890205301</v>
+      </c>
+      <c r="AE28">
+        <v>68.590525150299001</v>
       </c>
       <c r="AF28">
-        <v>138.64402890205301</v>
-      </c>
-      <c r="AG28">
-        <v>68.590525150299001</v>
-      </c>
-      <c r="AH28">
         <v>207.234554052352</v>
       </c>
     </row>
-    <row r="29" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>213</v>
+        <v>58</v>
       </c>
       <c r="B29">
         <v>30</v>
@@ -4446,25 +3813,19 @@
       <c r="AC29">
         <v>15</v>
       </c>
-      <c r="AD29" t="s">
-        <v>163</v>
-      </c>
-      <c r="AE29" t="s">
-        <v>1</v>
+      <c r="AD29">
+        <v>146.085395097732</v>
+      </c>
+      <c r="AE29">
+        <v>88.823225975036607</v>
       </c>
       <c r="AF29">
-        <v>146.085395097732</v>
-      </c>
-      <c r="AG29">
-        <v>88.823225975036607</v>
-      </c>
-      <c r="AH29">
         <v>234.90862107276899</v>
       </c>
     </row>
-    <row r="30" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>214</v>
+        <v>59</v>
       </c>
       <c r="B30">
         <v>30</v>
@@ -4551,25 +3912,19 @@
       <c r="AC30">
         <v>24</v>
       </c>
-      <c r="AD30" t="s">
-        <v>164</v>
-      </c>
-      <c r="AE30" t="s">
-        <v>3</v>
+      <c r="AD30">
+        <v>141.290609836578</v>
+      </c>
+      <c r="AE30">
+        <v>95.346505880355807</v>
       </c>
       <c r="AF30">
-        <v>141.290609836578</v>
-      </c>
-      <c r="AG30">
-        <v>95.346505880355807</v>
-      </c>
-      <c r="AH30">
         <v>236.63711571693401</v>
       </c>
     </row>
-    <row r="31" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>215</v>
+        <v>60</v>
       </c>
       <c r="B31">
         <v>30</v>
@@ -4656,25 +4011,19 @@
       <c r="AC31">
         <v>21</v>
       </c>
-      <c r="AD31" t="s">
-        <v>165</v>
-      </c>
-      <c r="AE31" t="s">
-        <v>1</v>
+      <c r="AD31">
+        <v>149.95642900466899</v>
+      </c>
+      <c r="AE31">
+        <v>143.743196010589</v>
       </c>
       <c r="AF31">
-        <v>149.95642900466899</v>
-      </c>
-      <c r="AG31">
-        <v>143.743196010589</v>
-      </c>
-      <c r="AH31">
         <v>293.69962501525799</v>
       </c>
     </row>
-    <row r="32" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>216</v>
+        <v>61</v>
       </c>
       <c r="B32">
         <v>40</v>
@@ -4761,25 +4110,19 @@
       <c r="AC32">
         <v>36</v>
       </c>
-      <c r="AD32" t="s">
-        <v>166</v>
-      </c>
-      <c r="AE32" t="s">
-        <v>3</v>
+      <c r="AD32">
+        <v>378.34629487991299</v>
+      </c>
+      <c r="AE32">
+        <v>142.81647491455001</v>
       </c>
       <c r="AF32">
-        <v>378.34629487991299</v>
-      </c>
-      <c r="AG32">
-        <v>142.81647491455001</v>
-      </c>
-      <c r="AH32">
         <v>521.162769794464</v>
       </c>
     </row>
-    <row r="33" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>217</v>
+        <v>62</v>
       </c>
       <c r="B33">
         <v>40</v>
@@ -4866,25 +4209,19 @@
       <c r="AC33">
         <v>35</v>
       </c>
-      <c r="AD33" t="s">
-        <v>167</v>
-      </c>
-      <c r="AE33" t="s">
-        <v>1</v>
+      <c r="AD33">
+        <v>452.62490177154501</v>
+      </c>
+      <c r="AE33">
+        <v>220.257317066192</v>
       </c>
       <c r="AF33">
-        <v>452.62490177154501</v>
-      </c>
-      <c r="AG33">
-        <v>220.257317066192</v>
-      </c>
-      <c r="AH33">
         <v>672.88221883773804</v>
       </c>
     </row>
-    <row r="34" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>218</v>
+        <v>63</v>
       </c>
       <c r="B34">
         <v>40</v>
@@ -4971,25 +4308,19 @@
       <c r="AC34">
         <v>14</v>
       </c>
-      <c r="AD34" t="s">
-        <v>168</v>
-      </c>
-      <c r="AE34" t="s">
-        <v>1</v>
+      <c r="AD34">
+        <v>468.61311721801701</v>
+      </c>
+      <c r="AE34">
+        <v>135.34647917747401</v>
       </c>
       <c r="AF34">
-        <v>468.61311721801701</v>
-      </c>
-      <c r="AG34">
-        <v>135.34647917747401</v>
-      </c>
-      <c r="AH34">
         <v>603.95959639549199</v>
       </c>
     </row>
-    <row r="35" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>219</v>
+        <v>64</v>
       </c>
       <c r="B35">
         <v>40</v>
@@ -5076,25 +4407,19 @@
       <c r="AC35">
         <v>24</v>
       </c>
-      <c r="AD35" t="s">
-        <v>169</v>
-      </c>
-      <c r="AE35" t="s">
-        <v>1</v>
+      <c r="AD35">
+        <v>450.65094494819601</v>
+      </c>
+      <c r="AE35">
+        <v>81.632426023483205</v>
       </c>
       <c r="AF35">
-        <v>450.65094494819601</v>
-      </c>
-      <c r="AG35">
-        <v>81.632426023483205</v>
-      </c>
-      <c r="AH35">
         <v>532.28337097167901</v>
       </c>
     </row>
-    <row r="36" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>220</v>
+        <v>65</v>
       </c>
       <c r="B36">
         <v>40</v>
@@ -5181,25 +4506,19 @@
       <c r="AC36">
         <v>15</v>
       </c>
-      <c r="AD36" t="s">
-        <v>170</v>
-      </c>
-      <c r="AE36" t="s">
-        <v>1</v>
+      <c r="AD36">
+        <v>459.37547707557599</v>
+      </c>
+      <c r="AE36">
+        <v>89.720136880874605</v>
       </c>
       <c r="AF36">
-        <v>459.37547707557599</v>
-      </c>
-      <c r="AG36">
-        <v>89.720136880874605</v>
-      </c>
-      <c r="AH36">
         <v>549.09561395645096</v>
       </c>
     </row>
-    <row r="37" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>221</v>
+        <v>66</v>
       </c>
       <c r="B37">
         <v>40</v>
@@ -5286,25 +4605,19 @@
       <c r="AC37">
         <v>27</v>
       </c>
-      <c r="AD37" t="s">
-        <v>171</v>
-      </c>
-      <c r="AE37" t="s">
-        <v>1</v>
+      <c r="AD37">
+        <v>502.58026814460698</v>
+      </c>
+      <c r="AE37">
+        <v>222.42066884040801</v>
       </c>
       <c r="AF37">
-        <v>502.58026814460698</v>
-      </c>
-      <c r="AG37">
-        <v>222.42066884040801</v>
-      </c>
-      <c r="AH37">
         <v>725.00093698501496</v>
       </c>
     </row>
-    <row r="38" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>222</v>
+        <v>67</v>
       </c>
       <c r="B38">
         <v>40</v>
@@ -5391,25 +4704,19 @@
       <c r="AC38">
         <v>28</v>
       </c>
-      <c r="AD38" t="s">
-        <v>172</v>
-      </c>
-      <c r="AE38" t="s">
-        <v>3</v>
+      <c r="AD38">
+        <v>565.15974211692799</v>
+      </c>
+      <c r="AE38">
+        <v>171.53467893600401</v>
       </c>
       <c r="AF38">
-        <v>565.15974211692799</v>
-      </c>
-      <c r="AG38">
-        <v>171.53467893600401</v>
-      </c>
-      <c r="AH38">
         <v>736.69442105293194</v>
       </c>
     </row>
-    <row r="39" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>223</v>
+        <v>68</v>
       </c>
       <c r="B39">
         <v>40</v>
@@ -5496,25 +4803,19 @@
       <c r="AC39">
         <v>21</v>
       </c>
-      <c r="AD39" t="s">
-        <v>173</v>
-      </c>
-      <c r="AE39" t="s">
-        <v>3</v>
+      <c r="AD39">
+        <v>417.55774021148602</v>
+      </c>
+      <c r="AE39">
+        <v>164.965266942977</v>
       </c>
       <c r="AF39">
-        <v>417.55774021148602</v>
-      </c>
-      <c r="AG39">
-        <v>164.965266942977</v>
-      </c>
-      <c r="AH39">
         <v>582.52300715446404</v>
       </c>
     </row>
-    <row r="40" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>224</v>
+        <v>69</v>
       </c>
       <c r="B40">
         <v>40</v>
@@ -5601,25 +4902,19 @@
       <c r="AC40">
         <v>28</v>
       </c>
-      <c r="AD40" t="s">
-        <v>174</v>
-      </c>
-      <c r="AE40" t="s">
-        <v>1</v>
+      <c r="AD40">
+        <v>407.20061278343201</v>
+      </c>
+      <c r="AE40">
+        <v>161.46263074874801</v>
       </c>
       <c r="AF40">
-        <v>407.20061278343201</v>
-      </c>
-      <c r="AG40">
-        <v>161.46263074874801</v>
-      </c>
-      <c r="AH40">
         <v>568.66324353217999</v>
       </c>
     </row>
-    <row r="41" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>225</v>
+        <v>70</v>
       </c>
       <c r="B41">
         <v>40</v>
@@ -5706,25 +5001,19 @@
       <c r="AC41">
         <v>29</v>
       </c>
-      <c r="AD41" t="s">
-        <v>175</v>
-      </c>
-      <c r="AE41" t="s">
-        <v>3</v>
+      <c r="AD41">
+        <v>420.29395818710299</v>
+      </c>
+      <c r="AE41">
+        <v>159.02583909034701</v>
       </c>
       <c r="AF41">
-        <v>420.29395818710299</v>
-      </c>
-      <c r="AG41">
-        <v>159.02583909034701</v>
-      </c>
-      <c r="AH41">
         <v>579.31979727744999</v>
       </c>
     </row>
-    <row r="42" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>226</v>
+        <v>71</v>
       </c>
       <c r="B42">
         <v>50</v>
@@ -5811,25 +5100,19 @@
       <c r="AC42">
         <v>29</v>
       </c>
-      <c r="AD42" t="s">
-        <v>176</v>
-      </c>
-      <c r="AE42" t="s">
-        <v>3</v>
+      <c r="AD42">
+        <v>954.258726119995</v>
+      </c>
+      <c r="AE42">
+        <v>182.79385805129999</v>
       </c>
       <c r="AF42">
-        <v>954.258726119995</v>
-      </c>
-      <c r="AG42">
-        <v>182.79385805129999</v>
-      </c>
-      <c r="AH42">
         <v>1137.0525841712899</v>
       </c>
     </row>
-    <row r="43" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>227</v>
+        <v>72</v>
       </c>
       <c r="B43">
         <v>50</v>
@@ -5916,25 +5199,19 @@
       <c r="AC43">
         <v>41</v>
       </c>
-      <c r="AD43" t="s">
-        <v>177</v>
-      </c>
-      <c r="AE43" t="s">
-        <v>1</v>
+      <c r="AD43">
+        <v>941.51287508010796</v>
+      </c>
+      <c r="AE43">
+        <v>293.762964963912</v>
       </c>
       <c r="AF43">
-        <v>941.51287508010796</v>
-      </c>
-      <c r="AG43">
-        <v>293.762964963912</v>
-      </c>
-      <c r="AH43">
         <v>1235.27584004402</v>
       </c>
     </row>
-    <row r="44" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>228</v>
+        <v>73</v>
       </c>
       <c r="B44">
         <v>50</v>
@@ -6021,25 +5298,19 @@
       <c r="AC44">
         <v>38</v>
       </c>
-      <c r="AD44" t="s">
-        <v>178</v>
-      </c>
-      <c r="AE44" t="s">
-        <v>3</v>
+      <c r="AD44">
+        <v>1158.0212471485099</v>
+      </c>
+      <c r="AE44">
+        <v>228.46899199485699</v>
       </c>
       <c r="AF44">
-        <v>1158.0212471485099</v>
-      </c>
-      <c r="AG44">
-        <v>228.46899199485699</v>
-      </c>
-      <c r="AH44">
         <v>1386.49023914337</v>
       </c>
     </row>
-    <row r="45" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>229</v>
+        <v>74</v>
       </c>
       <c r="B45">
         <v>50</v>
@@ -6126,25 +5397,19 @@
       <c r="AC45">
         <v>28</v>
       </c>
-      <c r="AD45" t="s">
-        <v>179</v>
-      </c>
-      <c r="AE45" t="s">
-        <v>3</v>
+      <c r="AD45">
+        <v>919.27295994758595</v>
+      </c>
+      <c r="AE45">
+        <v>194.61141109466499</v>
       </c>
       <c r="AF45">
-        <v>919.27295994758595</v>
-      </c>
-      <c r="AG45">
-        <v>194.61141109466499</v>
-      </c>
-      <c r="AH45">
         <v>1113.88437104225</v>
       </c>
     </row>
-    <row r="46" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>230</v>
+        <v>75</v>
       </c>
       <c r="B46">
         <v>50</v>
@@ -6231,25 +5496,19 @@
       <c r="AC46">
         <v>39</v>
       </c>
-      <c r="AD46" t="s">
-        <v>180</v>
-      </c>
-      <c r="AE46" t="s">
-        <v>3</v>
+      <c r="AD46">
+        <v>1272.3284952640499</v>
+      </c>
+      <c r="AE46">
+        <v>242.57301616668701</v>
       </c>
       <c r="AF46">
-        <v>1272.3284952640499</v>
-      </c>
-      <c r="AG46">
-        <v>242.57301616668701</v>
-      </c>
-      <c r="AH46">
         <v>1514.9015114307399</v>
       </c>
     </row>
-    <row r="47" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>231</v>
+        <v>76</v>
       </c>
       <c r="B47">
         <v>50</v>
@@ -6336,25 +5595,19 @@
       <c r="AC47">
         <v>40</v>
       </c>
-      <c r="AD47" t="s">
-        <v>181</v>
-      </c>
-      <c r="AE47" t="s">
-        <v>1</v>
+      <c r="AD47">
+        <v>1046.4700579643199</v>
+      </c>
+      <c r="AE47">
+        <v>126.953025102615</v>
       </c>
       <c r="AF47">
-        <v>1046.4700579643199</v>
-      </c>
-      <c r="AG47">
-        <v>126.953025102615</v>
-      </c>
-      <c r="AH47">
         <v>1173.4230830669401</v>
       </c>
     </row>
-    <row r="48" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>232</v>
+        <v>77</v>
       </c>
       <c r="B48">
         <v>50</v>
@@ -6441,25 +5694,19 @@
       <c r="AC48">
         <v>26</v>
       </c>
-      <c r="AD48" t="s">
-        <v>182</v>
-      </c>
-      <c r="AE48" t="s">
-        <v>3</v>
+      <c r="AD48">
+        <v>1086.7812922000801</v>
+      </c>
+      <c r="AE48">
+        <v>204.84176707267699</v>
       </c>
       <c r="AF48">
-        <v>1086.7812922000801</v>
-      </c>
-      <c r="AG48">
-        <v>204.84176707267699</v>
-      </c>
-      <c r="AH48">
         <v>1291.62305927276</v>
       </c>
     </row>
-    <row r="49" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>233</v>
+        <v>78</v>
       </c>
       <c r="B49">
         <v>50</v>
@@ -6546,25 +5793,19 @@
       <c r="AC49">
         <v>30</v>
       </c>
-      <c r="AD49" t="s">
-        <v>183</v>
-      </c>
-      <c r="AE49" t="s">
-        <v>3</v>
+      <c r="AD49">
+        <v>1236.7747070789301</v>
+      </c>
+      <c r="AE49">
+        <v>242.533853769302</v>
       </c>
       <c r="AF49">
-        <v>1236.7747070789301</v>
-      </c>
-      <c r="AG49">
-        <v>242.533853769302</v>
-      </c>
-      <c r="AH49">
         <v>1479.3085608482299</v>
       </c>
     </row>
-    <row r="50" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>234</v>
+        <v>79</v>
       </c>
       <c r="B50">
         <v>50</v>
@@ -6651,25 +5892,19 @@
       <c r="AC50">
         <v>33</v>
       </c>
-      <c r="AD50" t="s">
-        <v>184</v>
-      </c>
-      <c r="AE50" t="s">
-        <v>3</v>
+      <c r="AD50">
+        <v>1212.57941484451</v>
+      </c>
+      <c r="AE50">
+        <v>208.043116807937</v>
       </c>
       <c r="AF50">
-        <v>1212.57941484451</v>
-      </c>
-      <c r="AG50">
-        <v>208.043116807937</v>
-      </c>
-      <c r="AH50">
         <v>1420.6225316524501</v>
       </c>
     </row>
-    <row r="51" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>235</v>
+        <v>80</v>
       </c>
       <c r="B51">
         <v>50</v>
@@ -6756,19 +5991,13 @@
       <c r="AC51">
         <v>34</v>
       </c>
-      <c r="AD51" t="s">
-        <v>185</v>
-      </c>
-      <c r="AE51" t="s">
-        <v>3</v>
+      <c r="AD51">
+        <v>2211.6541802883098</v>
+      </c>
+      <c r="AE51">
+        <v>437.98937988281199</v>
       </c>
       <c r="AF51">
-        <v>2211.6541802883098</v>
-      </c>
-      <c r="AG51">
-        <v>437.98937988281199</v>
-      </c>
-      <c r="AH51">
         <v>2649.64356017112</v>
       </c>
     </row>
@@ -6779,113 +6008,107 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E3433D3-788D-5942-B1E2-D7BE09CA1D89}">
-  <dimension ref="A1:AH51"/>
+  <dimension ref="A1:AF51"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B1" t="s">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>55</v>
+        <v>1</v>
       </c>
       <c r="D1" t="s">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="E1" t="s">
-        <v>57</v>
+        <v>3</v>
       </c>
       <c r="F1" t="s">
-        <v>58</v>
+        <v>4</v>
       </c>
       <c r="G1" t="s">
-        <v>59</v>
+        <v>5</v>
       </c>
       <c r="H1" t="s">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="I1" t="s">
-        <v>61</v>
+        <v>7</v>
       </c>
       <c r="J1" t="s">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="K1" t="s">
-        <v>63</v>
+        <v>9</v>
       </c>
       <c r="L1" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
       <c r="M1" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="N1" t="s">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="O1" t="s">
-        <v>67</v>
+        <v>13</v>
       </c>
       <c r="P1" t="s">
-        <v>68</v>
+        <v>14</v>
       </c>
       <c r="Q1" t="s">
-        <v>69</v>
+        <v>15</v>
       </c>
       <c r="R1" t="s">
-        <v>70</v>
+        <v>16</v>
       </c>
       <c r="S1" t="s">
-        <v>71</v>
+        <v>17</v>
       </c>
       <c r="T1" t="s">
-        <v>72</v>
+        <v>18</v>
       </c>
       <c r="U1" t="s">
-        <v>73</v>
+        <v>19</v>
       </c>
       <c r="V1" t="s">
-        <v>74</v>
+        <v>20</v>
       </c>
       <c r="W1" t="s">
-        <v>75</v>
+        <v>21</v>
       </c>
       <c r="X1" t="s">
-        <v>76</v>
+        <v>22</v>
       </c>
       <c r="Y1" t="s">
-        <v>77</v>
+        <v>23</v>
       </c>
       <c r="Z1" t="s">
-        <v>78</v>
+        <v>24</v>
       </c>
       <c r="AA1" t="s">
-        <v>79</v>
+        <v>25</v>
       </c>
       <c r="AB1" t="s">
-        <v>80</v>
+        <v>26</v>
       </c>
       <c r="AC1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>81</v>
-      </c>
-      <c r="AD1" t="s">
-        <v>82</v>
-      </c>
-      <c r="AE1" t="s">
-        <v>83</v>
-      </c>
-      <c r="AF1" t="s">
-        <v>84</v>
-      </c>
-      <c r="AG1" t="s">
-        <v>85</v>
-      </c>
-      <c r="AH1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>236</v>
       </c>
       <c r="B2">
         <v>10</v>
@@ -6972,25 +6195,19 @@
       <c r="AC2">
         <v>7</v>
       </c>
-      <c r="AD2" t="s">
-        <v>87</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>12</v>
+      <c r="AD2">
+        <v>9.4157738685607892</v>
+      </c>
+      <c r="AE2">
+        <v>6.73197197914123</v>
       </c>
       <c r="AF2">
-        <v>9.4157738685607892</v>
-      </c>
-      <c r="AG2">
-        <v>6.73197197914123</v>
-      </c>
-      <c r="AH2">
         <v>16.147745847702001</v>
       </c>
     </row>
-    <row r="3" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>237</v>
+        <v>82</v>
       </c>
       <c r="B3">
         <v>10</v>
@@ -7077,25 +6294,19 @@
       <c r="AC3">
         <v>7</v>
       </c>
-      <c r="AD3" t="s">
-        <v>88</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>3</v>
+      <c r="AD3">
+        <v>9.8515148162841797</v>
+      </c>
+      <c r="AE3">
+        <v>3.3091731071472101</v>
       </c>
       <c r="AF3">
-        <v>9.8515148162841797</v>
-      </c>
-      <c r="AG3">
-        <v>3.3091731071472101</v>
-      </c>
-      <c r="AH3">
         <v>13.160687923431301</v>
       </c>
     </row>
-    <row r="4" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>238</v>
+        <v>83</v>
       </c>
       <c r="B4">
         <v>10</v>
@@ -7182,25 +6393,19 @@
       <c r="AC4">
         <v>3</v>
       </c>
-      <c r="AD4" t="s">
-        <v>89</v>
-      </c>
-      <c r="AE4" t="s">
-        <v>5</v>
+      <c r="AD4">
+        <v>11.014753103256201</v>
+      </c>
+      <c r="AE4">
+        <v>3.2985258102416899</v>
       </c>
       <c r="AF4">
-        <v>11.014753103256201</v>
-      </c>
-      <c r="AG4">
-        <v>3.2985258102416899</v>
-      </c>
-      <c r="AH4">
         <v>14.3132789134979</v>
       </c>
     </row>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>239</v>
+        <v>84</v>
       </c>
       <c r="B5">
         <v>10</v>
@@ -7287,25 +6492,19 @@
       <c r="AC5">
         <v>3</v>
       </c>
-      <c r="AD5" t="s">
-        <v>90</v>
-      </c>
-      <c r="AE5" t="s">
-        <v>3</v>
+      <c r="AD5">
+        <v>10.441143989562899</v>
+      </c>
+      <c r="AE5">
+        <v>3.3332419395446702</v>
       </c>
       <c r="AF5">
-        <v>10.441143989562899</v>
-      </c>
-      <c r="AG5">
-        <v>3.3332419395446702</v>
-      </c>
-      <c r="AH5">
         <v>13.7743859291076</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>240</v>
+        <v>85</v>
       </c>
       <c r="B6">
         <v>10</v>
@@ -7392,25 +6591,19 @@
       <c r="AC6">
         <v>8</v>
       </c>
-      <c r="AD6" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE6" t="s">
-        <v>3</v>
+      <c r="AD6">
+        <v>10.617235898971501</v>
+      </c>
+      <c r="AE6">
+        <v>4.52130103111267</v>
       </c>
       <c r="AF6">
-        <v>10.617235898971501</v>
-      </c>
-      <c r="AG6">
-        <v>4.52130103111267</v>
-      </c>
-      <c r="AH6">
         <v>15.1385369300842</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>241</v>
+        <v>86</v>
       </c>
       <c r="B7">
         <v>10</v>
@@ -7497,25 +6690,19 @@
       <c r="AC7">
         <v>4</v>
       </c>
-      <c r="AD7" t="s">
-        <v>92</v>
-      </c>
-      <c r="AE7" t="s">
-        <v>12</v>
+      <c r="AD7">
+        <v>9.5927319526672292</v>
+      </c>
+      <c r="AE7">
+        <v>5.0391590595245299</v>
       </c>
       <c r="AF7">
-        <v>9.5927319526672292</v>
-      </c>
-      <c r="AG7">
-        <v>5.0391590595245299</v>
-      </c>
-      <c r="AH7">
         <v>14.6318910121917</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>242</v>
+        <v>87</v>
       </c>
       <c r="B8">
         <v>10</v>
@@ -7602,25 +6789,19 @@
       <c r="AC8">
         <v>8</v>
       </c>
-      <c r="AD8" t="s">
-        <v>93</v>
-      </c>
-      <c r="AE8" t="s">
-        <v>1</v>
+      <c r="AD8">
+        <v>10.328311920166</v>
+      </c>
+      <c r="AE8">
+        <v>3.6347160339355402</v>
       </c>
       <c r="AF8">
-        <v>10.328311920166</v>
-      </c>
-      <c r="AG8">
-        <v>3.6347160339355402</v>
-      </c>
-      <c r="AH8">
         <v>13.9630279541015</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>243</v>
+        <v>88</v>
       </c>
       <c r="B9">
         <v>10</v>
@@ -7707,25 +6888,19 @@
       <c r="AC9">
         <v>5</v>
       </c>
-      <c r="AD9" t="s">
-        <v>94</v>
-      </c>
-      <c r="AE9" t="s">
-        <v>1</v>
+      <c r="AD9">
+        <v>10.0074870586395</v>
+      </c>
+      <c r="AE9">
+        <v>3.2607560157775799</v>
       </c>
       <c r="AF9">
-        <v>10.0074870586395</v>
-      </c>
-      <c r="AG9">
-        <v>3.2607560157775799</v>
-      </c>
-      <c r="AH9">
         <v>13.2682430744171</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>244</v>
+        <v>89</v>
       </c>
       <c r="B10">
         <v>10</v>
@@ -7812,25 +6987,19 @@
       <c r="AC10">
         <v>8</v>
       </c>
-      <c r="AD10" t="s">
-        <v>95</v>
-      </c>
-      <c r="AE10" t="s">
-        <v>3</v>
+      <c r="AD10">
+        <v>10.816698074340801</v>
+      </c>
+      <c r="AE10">
+        <v>3.4957127571105899</v>
       </c>
       <c r="AF10">
-        <v>10.816698074340801</v>
-      </c>
-      <c r="AG10">
-        <v>3.4957127571105899</v>
-      </c>
-      <c r="AH10">
         <v>14.3124108314514</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>245</v>
+        <v>90</v>
       </c>
       <c r="B11">
         <v>10</v>
@@ -7917,25 +7086,19 @@
       <c r="AC11">
         <v>6</v>
       </c>
-      <c r="AD11" t="s">
-        <v>96</v>
-      </c>
-      <c r="AE11" t="s">
-        <v>1</v>
+      <c r="AD11">
+        <v>11.138522863387999</v>
+      </c>
+      <c r="AE11">
+        <v>5.9777960777282697</v>
       </c>
       <c r="AF11">
-        <v>11.138522863387999</v>
-      </c>
-      <c r="AG11">
-        <v>5.9777960777282697</v>
-      </c>
-      <c r="AH11">
         <v>17.116318941116301</v>
       </c>
     </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>246</v>
+        <v>91</v>
       </c>
       <c r="B12">
         <v>20</v>
@@ -8022,25 +7185,19 @@
       <c r="AC12">
         <v>13</v>
       </c>
-      <c r="AD12" t="s">
-        <v>97</v>
-      </c>
-      <c r="AE12" t="s">
-        <v>1</v>
+      <c r="AD12">
+        <v>49.551102876663201</v>
+      </c>
+      <c r="AE12">
+        <v>11.9531209468841</v>
       </c>
       <c r="AF12">
-        <v>49.551102876663201</v>
-      </c>
-      <c r="AG12">
-        <v>11.9531209468841</v>
-      </c>
-      <c r="AH12">
         <v>61.504223823547299</v>
       </c>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>247</v>
+        <v>92</v>
       </c>
       <c r="B13">
         <v>20</v>
@@ -8127,25 +7284,19 @@
       <c r="AC13">
         <v>18</v>
       </c>
-      <c r="AD13" t="s">
-        <v>98</v>
-      </c>
-      <c r="AE13" t="s">
-        <v>3</v>
+      <c r="AD13">
+        <v>45.808905839920001</v>
+      </c>
+      <c r="AE13">
+        <v>36.437552213668802</v>
       </c>
       <c r="AF13">
-        <v>45.808905839920001</v>
-      </c>
-      <c r="AG13">
-        <v>36.437552213668802</v>
-      </c>
-      <c r="AH13">
         <v>82.246458053588796</v>
       </c>
     </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>248</v>
+        <v>93</v>
       </c>
       <c r="B14">
         <v>20</v>
@@ -8232,25 +7383,19 @@
       <c r="AC14">
         <v>18</v>
       </c>
-      <c r="AD14" t="s">
-        <v>99</v>
-      </c>
-      <c r="AE14" t="s">
-        <v>1</v>
+      <c r="AD14">
+        <v>40.198330879211397</v>
+      </c>
+      <c r="AE14">
+        <v>27.287709236145002</v>
       </c>
       <c r="AF14">
-        <v>40.198330879211397</v>
-      </c>
-      <c r="AG14">
-        <v>27.287709236145002</v>
-      </c>
-      <c r="AH14">
         <v>67.486040115356403</v>
       </c>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>249</v>
+        <v>94</v>
       </c>
       <c r="B15">
         <v>20</v>
@@ -8337,25 +7482,19 @@
       <c r="AC15">
         <v>11</v>
       </c>
-      <c r="AD15" t="s">
-        <v>100</v>
-      </c>
-      <c r="AE15" t="s">
-        <v>1</v>
+      <c r="AD15">
+        <v>43.748957157135003</v>
+      </c>
+      <c r="AE15">
+        <v>13.7379777431488</v>
       </c>
       <c r="AF15">
-        <v>43.748957157135003</v>
-      </c>
-      <c r="AG15">
-        <v>13.7379777431488</v>
-      </c>
-      <c r="AH15">
         <v>57.486934900283799</v>
       </c>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>250</v>
+        <v>95</v>
       </c>
       <c r="B16">
         <v>20</v>
@@ -8442,25 +7581,19 @@
       <c r="AC16">
         <v>11</v>
       </c>
-      <c r="AD16" t="s">
-        <v>101</v>
-      </c>
-      <c r="AE16" t="s">
-        <v>1</v>
+      <c r="AD16">
+        <v>47.645012140273998</v>
+      </c>
+      <c r="AE16">
+        <v>23.752976894378602</v>
       </c>
       <c r="AF16">
-        <v>47.645012140273998</v>
-      </c>
-      <c r="AG16">
-        <v>23.752976894378602</v>
-      </c>
-      <c r="AH16">
         <v>71.397989034652696</v>
       </c>
     </row>
-    <row r="17" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>251</v>
+        <v>96</v>
       </c>
       <c r="B17">
         <v>20</v>
@@ -8547,25 +7680,19 @@
       <c r="AC17">
         <v>6</v>
       </c>
-      <c r="AD17" t="s">
-        <v>102</v>
-      </c>
-      <c r="AE17" t="s">
-        <v>1</v>
+      <c r="AD17">
+        <v>43.0557732582092</v>
+      </c>
+      <c r="AE17">
+        <v>18.111796140670702</v>
       </c>
       <c r="AF17">
-        <v>43.0557732582092</v>
-      </c>
-      <c r="AG17">
-        <v>18.111796140670702</v>
-      </c>
-      <c r="AH17">
         <v>61.167569398879998</v>
       </c>
     </row>
-    <row r="18" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>252</v>
+        <v>97</v>
       </c>
       <c r="B18">
         <v>20</v>
@@ -8652,25 +7779,19 @@
       <c r="AC18">
         <v>17</v>
       </c>
-      <c r="AD18" t="s">
-        <v>103</v>
-      </c>
-      <c r="AE18" t="s">
-        <v>3</v>
+      <c r="AD18">
+        <v>46.391394138336103</v>
+      </c>
+      <c r="AE18">
+        <v>29.880862951278601</v>
       </c>
       <c r="AF18">
-        <v>46.391394138336103</v>
-      </c>
-      <c r="AG18">
-        <v>29.880862951278601</v>
-      </c>
-      <c r="AH18">
         <v>76.272257089614797</v>
       </c>
     </row>
-    <row r="19" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>253</v>
+        <v>98</v>
       </c>
       <c r="B19">
         <v>20</v>
@@ -8757,25 +7878,19 @@
       <c r="AC19">
         <v>13</v>
       </c>
-      <c r="AD19" t="s">
-        <v>104</v>
-      </c>
-      <c r="AE19" t="s">
-        <v>1</v>
+      <c r="AD19">
+        <v>45.5163249969482</v>
+      </c>
+      <c r="AE19">
+        <v>23.103228807449302</v>
       </c>
       <c r="AF19">
-        <v>45.5163249969482</v>
-      </c>
-      <c r="AG19">
-        <v>23.103228807449302</v>
-      </c>
-      <c r="AH19">
         <v>68.619553804397498</v>
       </c>
     </row>
-    <row r="20" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>254</v>
+        <v>99</v>
       </c>
       <c r="B20">
         <v>20</v>
@@ -8862,25 +7977,19 @@
       <c r="AC20">
         <v>15</v>
       </c>
-      <c r="AD20" t="s">
-        <v>105</v>
-      </c>
-      <c r="AE20" t="s">
-        <v>1</v>
+      <c r="AD20">
+        <v>47.289702177047701</v>
+      </c>
+      <c r="AE20">
+        <v>20.458860874176001</v>
       </c>
       <c r="AF20">
-        <v>47.289702177047701</v>
-      </c>
-      <c r="AG20">
-        <v>20.458860874176001</v>
-      </c>
-      <c r="AH20">
         <v>67.748563051223698</v>
       </c>
     </row>
-    <row r="21" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>255</v>
+        <v>100</v>
       </c>
       <c r="B21">
         <v>20</v>
@@ -8967,25 +8076,19 @@
       <c r="AC21">
         <v>13</v>
       </c>
-      <c r="AD21" t="s">
-        <v>106</v>
-      </c>
-      <c r="AE21" t="s">
-        <v>1</v>
+      <c r="AD21">
+        <v>47.1596231460571</v>
+      </c>
+      <c r="AE21">
+        <v>30.8250617980957</v>
       </c>
       <c r="AF21">
-        <v>47.1596231460571</v>
-      </c>
-      <c r="AG21">
-        <v>30.8250617980957</v>
-      </c>
-      <c r="AH21">
         <v>77.984684944152804</v>
       </c>
     </row>
-    <row r="22" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>256</v>
+        <v>101</v>
       </c>
       <c r="B22">
         <v>30</v>
@@ -9072,25 +8175,19 @@
       <c r="AC22">
         <v>10</v>
       </c>
-      <c r="AD22" t="s">
-        <v>107</v>
-      </c>
-      <c r="AE22" t="s">
-        <v>1</v>
+      <c r="AD22">
+        <v>135.55315089225701</v>
+      </c>
+      <c r="AE22">
+        <v>38.167981147766099</v>
       </c>
       <c r="AF22">
-        <v>135.55315089225701</v>
-      </c>
-      <c r="AG22">
-        <v>38.167981147766099</v>
-      </c>
-      <c r="AH22">
         <v>173.72113204002301</v>
       </c>
     </row>
-    <row r="23" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>257</v>
+        <v>102</v>
       </c>
       <c r="B23">
         <v>30</v>
@@ -9177,25 +8274,19 @@
       <c r="AC23">
         <v>15</v>
       </c>
-      <c r="AD23" t="s">
-        <v>108</v>
-      </c>
-      <c r="AE23" t="s">
-        <v>1</v>
+      <c r="AD23">
+        <v>124.851977825164</v>
+      </c>
+      <c r="AE23">
+        <v>62.759104013442901</v>
       </c>
       <c r="AF23">
-        <v>124.851977825164</v>
-      </c>
-      <c r="AG23">
-        <v>62.759104013442901</v>
-      </c>
-      <c r="AH23">
         <v>187.61108183860699</v>
       </c>
     </row>
-    <row r="24" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>258</v>
+        <v>103</v>
       </c>
       <c r="B24">
         <v>30</v>
@@ -9282,25 +8373,19 @@
       <c r="AC24">
         <v>16</v>
       </c>
-      <c r="AD24" t="s">
-        <v>109</v>
-      </c>
-      <c r="AE24" t="s">
-        <v>1</v>
+      <c r="AD24">
+        <v>127.552557945251</v>
+      </c>
+      <c r="AE24">
+        <v>54.779661893844597</v>
       </c>
       <c r="AF24">
-        <v>127.552557945251</v>
-      </c>
-      <c r="AG24">
-        <v>54.779661893844597</v>
-      </c>
-      <c r="AH24">
         <v>182.33221983909601</v>
       </c>
     </row>
-    <row r="25" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>259</v>
+        <v>104</v>
       </c>
       <c r="B25">
         <v>30</v>
@@ -9387,25 +8472,19 @@
       <c r="AC25">
         <v>28</v>
       </c>
-      <c r="AD25" t="s">
-        <v>110</v>
-      </c>
-      <c r="AE25" t="s">
-        <v>1</v>
+      <c r="AD25">
+        <v>127.286892175674</v>
+      </c>
+      <c r="AE25">
+        <v>75.431526184082003</v>
       </c>
       <c r="AF25">
-        <v>127.286892175674</v>
-      </c>
-      <c r="AG25">
-        <v>75.431526184082003</v>
-      </c>
-      <c r="AH25">
         <v>202.71841835975599</v>
       </c>
     </row>
-    <row r="26" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>260</v>
+        <v>105</v>
       </c>
       <c r="B26">
         <v>30</v>
@@ -9492,25 +8571,19 @@
       <c r="AC26">
         <v>19</v>
       </c>
-      <c r="AD26" t="s">
-        <v>111</v>
-      </c>
-      <c r="AE26" t="s">
-        <v>1</v>
+      <c r="AD26">
+        <v>116.23481011390599</v>
+      </c>
+      <c r="AE26">
+        <v>53.9560062885284</v>
       </c>
       <c r="AF26">
-        <v>116.23481011390599</v>
-      </c>
-      <c r="AG26">
-        <v>53.9560062885284</v>
-      </c>
-      <c r="AH26">
         <v>170.19081640243499</v>
       </c>
     </row>
-    <row r="27" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>261</v>
+        <v>106</v>
       </c>
       <c r="B27">
         <v>30</v>
@@ -9597,25 +8670,19 @@
       <c r="AC27">
         <v>14</v>
       </c>
-      <c r="AD27" t="s">
-        <v>112</v>
-      </c>
-      <c r="AE27" t="s">
-        <v>3</v>
+      <c r="AD27">
+        <v>145.68524909019399</v>
+      </c>
+      <c r="AE27">
+        <v>25.316016912460299</v>
       </c>
       <c r="AF27">
-        <v>145.68524909019399</v>
-      </c>
-      <c r="AG27">
-        <v>25.316016912460299</v>
-      </c>
-      <c r="AH27">
         <v>171.001266002655</v>
       </c>
     </row>
-    <row r="28" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>262</v>
+        <v>107</v>
       </c>
       <c r="B28">
         <v>30</v>
@@ -9702,25 +8769,19 @@
       <c r="AC28">
         <v>20</v>
       </c>
-      <c r="AD28" t="s">
-        <v>113</v>
-      </c>
-      <c r="AE28" t="s">
-        <v>1</v>
+      <c r="AD28">
+        <v>135.87075805664</v>
+      </c>
+      <c r="AE28">
+        <v>50.742400884628204</v>
       </c>
       <c r="AF28">
-        <v>135.87075805664</v>
-      </c>
-      <c r="AG28">
-        <v>50.742400884628204</v>
-      </c>
-      <c r="AH28">
         <v>186.61315894126801</v>
       </c>
     </row>
-    <row r="29" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>263</v>
+        <v>108</v>
       </c>
       <c r="B29">
         <v>30</v>
@@ -9807,25 +8868,19 @@
       <c r="AC29">
         <v>26</v>
       </c>
-      <c r="AD29" t="s">
-        <v>114</v>
-      </c>
-      <c r="AE29" t="s">
-        <v>1</v>
+      <c r="AD29">
+        <v>119.642781972885</v>
+      </c>
+      <c r="AE29">
+        <v>80.526319980621295</v>
       </c>
       <c r="AF29">
-        <v>119.642781972885</v>
-      </c>
-      <c r="AG29">
-        <v>80.526319980621295</v>
-      </c>
-      <c r="AH29">
         <v>200.16910195350599</v>
       </c>
     </row>
-    <row r="30" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>264</v>
+        <v>109</v>
       </c>
       <c r="B30">
         <v>30</v>
@@ -9912,25 +8967,19 @@
       <c r="AC30">
         <v>21</v>
       </c>
-      <c r="AD30" t="s">
-        <v>115</v>
-      </c>
-      <c r="AE30" t="s">
-        <v>3</v>
+      <c r="AD30">
+        <v>128.41900897025999</v>
+      </c>
+      <c r="AE30">
+        <v>91.240597009658799</v>
       </c>
       <c r="AF30">
-        <v>128.41900897025999</v>
-      </c>
-      <c r="AG30">
-        <v>91.240597009658799</v>
-      </c>
-      <c r="AH30">
         <v>219.65960597991901</v>
       </c>
     </row>
-    <row r="31" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>265</v>
+        <v>110</v>
       </c>
       <c r="B31">
         <v>30</v>
@@ -10017,25 +9066,19 @@
       <c r="AC31">
         <v>16</v>
       </c>
-      <c r="AD31" t="s">
-        <v>116</v>
-      </c>
-      <c r="AE31" t="s">
-        <v>12</v>
+      <c r="AD31">
+        <v>149.09153819084099</v>
+      </c>
+      <c r="AE31">
+        <v>63.388777256011899</v>
       </c>
       <c r="AF31">
-        <v>149.09153819084099</v>
-      </c>
-      <c r="AG31">
-        <v>63.388777256011899</v>
-      </c>
-      <c r="AH31">
         <v>212.48031544685301</v>
       </c>
     </row>
-    <row r="32" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>266</v>
+        <v>111</v>
       </c>
       <c r="B32">
         <v>40</v>
@@ -10122,25 +9165,19 @@
       <c r="AC32">
         <v>16</v>
       </c>
-      <c r="AD32" t="s">
-        <v>117</v>
-      </c>
-      <c r="AE32" t="s">
-        <v>1</v>
+      <c r="AD32">
+        <v>449.83629179000798</v>
+      </c>
+      <c r="AE32">
+        <v>98.252974033355699</v>
       </c>
       <c r="AF32">
-        <v>449.83629179000798</v>
-      </c>
-      <c r="AG32">
-        <v>98.252974033355699</v>
-      </c>
-      <c r="AH32">
         <v>548.08926582336403</v>
       </c>
     </row>
-    <row r="33" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>267</v>
+        <v>112</v>
       </c>
       <c r="B33">
         <v>40</v>
@@ -10227,25 +9264,19 @@
       <c r="AC33">
         <v>22</v>
       </c>
-      <c r="AD33" t="s">
-        <v>118</v>
-      </c>
-      <c r="AE33" t="s">
-        <v>1</v>
+      <c r="AD33">
+        <v>426.20470571517899</v>
+      </c>
+      <c r="AE33">
+        <v>113.604616403579</v>
       </c>
       <c r="AF33">
-        <v>426.20470571517899</v>
-      </c>
-      <c r="AG33">
-        <v>113.604616403579</v>
-      </c>
-      <c r="AH33">
         <v>539.80932211875904</v>
       </c>
     </row>
-    <row r="34" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>268</v>
+        <v>113</v>
       </c>
       <c r="B34">
         <v>40</v>
@@ -10332,25 +9363,19 @@
       <c r="AC34">
         <v>27</v>
       </c>
-      <c r="AD34" t="s">
-        <v>119</v>
-      </c>
-      <c r="AE34" t="s">
-        <v>3</v>
+      <c r="AD34">
+        <v>502.795662164688</v>
+      </c>
+      <c r="AE34">
+        <v>140.11027097702001</v>
       </c>
       <c r="AF34">
-        <v>502.795662164688</v>
-      </c>
-      <c r="AG34">
-        <v>140.11027097702001</v>
-      </c>
-      <c r="AH34">
         <v>642.90593314170803</v>
       </c>
     </row>
-    <row r="35" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>269</v>
+        <v>114</v>
       </c>
       <c r="B35">
         <v>40</v>
@@ -10437,25 +9462,19 @@
       <c r="AC35">
         <v>30</v>
       </c>
-      <c r="AD35" t="s">
-        <v>120</v>
-      </c>
-      <c r="AE35" t="s">
-        <v>1</v>
+      <c r="AD35">
+        <v>402.56162381172101</v>
+      </c>
+      <c r="AE35">
+        <v>111.536049365997</v>
       </c>
       <c r="AF35">
-        <v>402.56162381172101</v>
-      </c>
-      <c r="AG35">
-        <v>111.536049365997</v>
-      </c>
-      <c r="AH35">
         <v>514.097673177719</v>
       </c>
     </row>
-    <row r="36" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>270</v>
+        <v>115</v>
       </c>
       <c r="B36">
         <v>40</v>
@@ -10542,25 +9561,19 @@
       <c r="AC36">
         <v>28</v>
       </c>
-      <c r="AD36" t="s">
-        <v>121</v>
-      </c>
-      <c r="AE36" t="s">
-        <v>1</v>
+      <c r="AD36">
+        <v>391.98561286926201</v>
+      </c>
+      <c r="AE36">
+        <v>103.061362028121</v>
       </c>
       <c r="AF36">
-        <v>391.98561286926201</v>
-      </c>
-      <c r="AG36">
-        <v>103.061362028121</v>
-      </c>
-      <c r="AH36">
         <v>495.04697489738402</v>
       </c>
     </row>
-    <row r="37" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>271</v>
+        <v>116</v>
       </c>
       <c r="B37">
         <v>40</v>
@@ -10647,25 +9660,19 @@
       <c r="AC37">
         <v>22</v>
       </c>
-      <c r="AD37" t="s">
-        <v>122</v>
-      </c>
-      <c r="AE37" t="s">
-        <v>12</v>
+      <c r="AD37">
+        <v>366.50295400619501</v>
+      </c>
+      <c r="AE37">
+        <v>94.317531108856201</v>
       </c>
       <c r="AF37">
-        <v>366.50295400619501</v>
-      </c>
-      <c r="AG37">
-        <v>94.317531108856201</v>
-      </c>
-      <c r="AH37">
         <v>460.82048511505099</v>
       </c>
     </row>
-    <row r="38" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>272</v>
+        <v>117</v>
       </c>
       <c r="B38">
         <v>40</v>
@@ -10752,25 +9759,19 @@
       <c r="AC38">
         <v>23</v>
       </c>
-      <c r="AD38" t="s">
-        <v>123</v>
-      </c>
-      <c r="AE38" t="s">
-        <v>1</v>
+      <c r="AD38">
+        <v>409.32594680786099</v>
+      </c>
+      <c r="AE38">
+        <v>106.229755878448</v>
       </c>
       <c r="AF38">
-        <v>409.32594680786099</v>
-      </c>
-      <c r="AG38">
-        <v>106.229755878448</v>
-      </c>
-      <c r="AH38">
         <v>515.55570268630902</v>
       </c>
     </row>
-    <row r="39" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>273</v>
+        <v>118</v>
       </c>
       <c r="B39">
         <v>40</v>
@@ -10857,25 +9858,19 @@
       <c r="AC39">
         <v>16</v>
       </c>
-      <c r="AD39" t="s">
-        <v>124</v>
-      </c>
-      <c r="AE39" t="s">
-        <v>12</v>
+      <c r="AD39">
+        <v>427.67327618598898</v>
+      </c>
+      <c r="AE39">
+        <v>79.586361885070801</v>
       </c>
       <c r="AF39">
-        <v>427.67327618598898</v>
-      </c>
-      <c r="AG39">
-        <v>79.586361885070801</v>
-      </c>
-      <c r="AH39">
         <v>507.25963807106001</v>
       </c>
     </row>
-    <row r="40" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>274</v>
+        <v>119</v>
       </c>
       <c r="B40">
         <v>40</v>
@@ -10962,25 +9957,19 @@
       <c r="AC40">
         <v>23</v>
       </c>
-      <c r="AD40" t="s">
-        <v>125</v>
-      </c>
-      <c r="AE40" t="s">
-        <v>12</v>
+      <c r="AD40">
+        <v>446.67418003082201</v>
+      </c>
+      <c r="AE40">
+        <v>117.826289892196</v>
       </c>
       <c r="AF40">
-        <v>446.67418003082201</v>
-      </c>
-      <c r="AG40">
-        <v>117.826289892196</v>
-      </c>
-      <c r="AH40">
         <v>564.50046992301895</v>
       </c>
     </row>
-    <row r="41" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>275</v>
+        <v>120</v>
       </c>
       <c r="B41">
         <v>40</v>
@@ -11067,25 +10056,19 @@
       <c r="AC41">
         <v>26</v>
       </c>
-      <c r="AD41" t="s">
-        <v>126</v>
-      </c>
-      <c r="AE41" t="s">
-        <v>3</v>
+      <c r="AD41">
+        <v>395.07055425643898</v>
+      </c>
+      <c r="AE41">
+        <v>116.737749099731</v>
       </c>
       <c r="AF41">
-        <v>395.07055425643898</v>
-      </c>
-      <c r="AG41">
-        <v>116.737749099731</v>
-      </c>
-      <c r="AH41">
         <v>511.80830335616997</v>
       </c>
     </row>
-    <row r="42" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>276</v>
+        <v>121</v>
       </c>
       <c r="B42">
         <v>50</v>
@@ -11172,25 +10155,19 @@
       <c r="AC42">
         <v>23</v>
       </c>
-      <c r="AD42" t="s">
-        <v>127</v>
-      </c>
-      <c r="AE42" t="s">
-        <v>1</v>
+      <c r="AD42">
+        <v>1072.28941178321</v>
+      </c>
+      <c r="AE42">
+        <v>148.19584822654701</v>
       </c>
       <c r="AF42">
-        <v>1072.28941178321</v>
-      </c>
-      <c r="AG42">
-        <v>148.19584822654701</v>
-      </c>
-      <c r="AH42">
         <v>1220.4852600097599</v>
       </c>
     </row>
-    <row r="43" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>277</v>
+        <v>122</v>
       </c>
       <c r="B43">
         <v>50</v>
@@ -11277,25 +10254,19 @@
       <c r="AC43">
         <v>26</v>
       </c>
-      <c r="AD43" t="s">
-        <v>128</v>
-      </c>
-      <c r="AE43" t="s">
-        <v>1</v>
+      <c r="AD43">
+        <v>1282.4070510864201</v>
+      </c>
+      <c r="AE43">
+        <v>167.43449306488</v>
       </c>
       <c r="AF43">
-        <v>1282.4070510864201</v>
-      </c>
-      <c r="AG43">
-        <v>167.43449306488</v>
-      </c>
-      <c r="AH43">
         <v>1449.8415441513</v>
       </c>
     </row>
-    <row r="44" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>278</v>
+        <v>123</v>
       </c>
       <c r="B44">
         <v>50</v>
@@ -11382,25 +10353,19 @@
       <c r="AC44">
         <v>32</v>
       </c>
-      <c r="AD44" t="s">
-        <v>129</v>
-      </c>
-      <c r="AE44" t="s">
-        <v>3</v>
+      <c r="AD44">
+        <v>1298.06647801399</v>
+      </c>
+      <c r="AE44">
+        <v>176.93713808059599</v>
       </c>
       <c r="AF44">
-        <v>1298.06647801399</v>
-      </c>
-      <c r="AG44">
-        <v>176.93713808059599</v>
-      </c>
-      <c r="AH44">
         <v>1475.0036160945799</v>
       </c>
     </row>
-    <row r="45" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>279</v>
+        <v>124</v>
       </c>
       <c r="B45">
         <v>50</v>
@@ -11487,25 +10452,19 @@
       <c r="AC45">
         <v>32</v>
       </c>
-      <c r="AD45" t="s">
-        <v>130</v>
-      </c>
-      <c r="AE45" t="s">
-        <v>1</v>
+      <c r="AD45">
+        <v>940.62508082389797</v>
+      </c>
+      <c r="AE45">
+        <v>162.05153989791799</v>
       </c>
       <c r="AF45">
-        <v>940.62508082389797</v>
-      </c>
-      <c r="AG45">
-        <v>162.05153989791799</v>
-      </c>
-      <c r="AH45">
         <v>1102.67662072181</v>
       </c>
     </row>
-    <row r="46" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>280</v>
+        <v>125</v>
       </c>
       <c r="B46">
         <v>50</v>
@@ -11592,25 +10551,19 @@
       <c r="AC46">
         <v>39</v>
       </c>
-      <c r="AD46" t="s">
-        <v>131</v>
-      </c>
-      <c r="AE46" t="s">
-        <v>12</v>
+      <c r="AD46">
+        <v>1238.9080979824</v>
+      </c>
+      <c r="AE46">
+        <v>178.90342712402301</v>
       </c>
       <c r="AF46">
-        <v>1238.9080979824</v>
-      </c>
-      <c r="AG46">
-        <v>178.90342712402301</v>
-      </c>
-      <c r="AH46">
         <v>1417.8115251064301</v>
       </c>
     </row>
-    <row r="47" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>281</v>
+        <v>126</v>
       </c>
       <c r="B47">
         <v>50</v>
@@ -11697,25 +10650,19 @@
       <c r="AC47">
         <v>27</v>
       </c>
-      <c r="AD47" t="s">
-        <v>132</v>
-      </c>
-      <c r="AE47" t="s">
-        <v>1</v>
+      <c r="AD47">
+        <v>1228.12793898582</v>
+      </c>
+      <c r="AE47">
+        <v>161.990744829177</v>
       </c>
       <c r="AF47">
-        <v>1228.12793898582</v>
-      </c>
-      <c r="AG47">
-        <v>161.990744829177</v>
-      </c>
-      <c r="AH47">
         <v>1390.1186838149999</v>
       </c>
     </row>
-    <row r="48" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>282</v>
+        <v>127</v>
       </c>
       <c r="B48">
         <v>50</v>
@@ -11802,25 +10749,19 @@
       <c r="AC48">
         <v>33</v>
       </c>
-      <c r="AD48" t="s">
-        <v>133</v>
-      </c>
-      <c r="AE48" t="s">
-        <v>3</v>
+      <c r="AD48">
+        <v>1098.0026500224999</v>
+      </c>
+      <c r="AE48">
+        <v>208.693424224853</v>
       </c>
       <c r="AF48">
-        <v>1098.0026500224999</v>
-      </c>
-      <c r="AG48">
-        <v>208.693424224853</v>
-      </c>
-      <c r="AH48">
         <v>1306.69607424736</v>
       </c>
     </row>
-    <row r="49" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>283</v>
+        <v>128</v>
       </c>
       <c r="B49">
         <v>50</v>
@@ -11907,25 +10848,19 @@
       <c r="AC49">
         <v>40</v>
       </c>
-      <c r="AD49" t="s">
-        <v>134</v>
-      </c>
-      <c r="AE49" t="s">
-        <v>1</v>
+      <c r="AD49">
+        <v>934.84503889083805</v>
+      </c>
+      <c r="AE49">
+        <v>228.66733813285799</v>
       </c>
       <c r="AF49">
-        <v>934.84503889083805</v>
-      </c>
-      <c r="AG49">
-        <v>228.66733813285799</v>
-      </c>
-      <c r="AH49">
         <v>1163.5123770236901</v>
       </c>
     </row>
-    <row r="50" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>284</v>
+        <v>129</v>
       </c>
       <c r="B50">
         <v>50</v>
@@ -12012,25 +10947,19 @@
       <c r="AC50">
         <v>29</v>
       </c>
-      <c r="AD50" t="s">
-        <v>135</v>
-      </c>
-      <c r="AE50" t="s">
-        <v>3</v>
+      <c r="AD50">
+        <v>1272.6692790985101</v>
+      </c>
+      <c r="AE50">
+        <v>179.06308102607699</v>
       </c>
       <c r="AF50">
-        <v>1272.6692790985101</v>
-      </c>
-      <c r="AG50">
-        <v>179.06308102607699</v>
-      </c>
-      <c r="AH50">
         <v>1451.7323601245801</v>
       </c>
     </row>
-    <row r="51" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>285</v>
+        <v>130</v>
       </c>
       <c r="B51">
         <v>50</v>
@@ -12117,19 +11046,13 @@
       <c r="AC51">
         <v>32</v>
       </c>
-      <c r="AD51" t="s">
-        <v>136</v>
-      </c>
-      <c r="AE51" t="s">
-        <v>1</v>
+      <c r="AD51">
+        <v>1068.6362309455801</v>
+      </c>
+      <c r="AE51">
+        <v>117.832195043563</v>
       </c>
       <c r="AF51">
-        <v>1068.6362309455801</v>
-      </c>
-      <c r="AG51">
-        <v>117.832195043563</v>
-      </c>
-      <c r="AH51">
         <v>1186.4684259891501</v>
       </c>
     </row>
@@ -12140,113 +11063,107 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15C29108-4C5D-F943-AE59-BB1B727CA2C9}">
-  <dimension ref="A1:AH51"/>
+  <dimension ref="A1:AF51"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B1" t="s">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>55</v>
+        <v>1</v>
       </c>
       <c r="D1" t="s">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="E1" t="s">
-        <v>57</v>
+        <v>3</v>
       </c>
       <c r="F1" t="s">
-        <v>58</v>
+        <v>4</v>
       </c>
       <c r="G1" t="s">
-        <v>59</v>
+        <v>5</v>
       </c>
       <c r="H1" t="s">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="I1" t="s">
-        <v>61</v>
+        <v>7</v>
       </c>
       <c r="J1" t="s">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="K1" t="s">
-        <v>63</v>
+        <v>9</v>
       </c>
       <c r="L1" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
       <c r="M1" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="N1" t="s">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="O1" t="s">
-        <v>67</v>
+        <v>13</v>
       </c>
       <c r="P1" t="s">
-        <v>68</v>
+        <v>14</v>
       </c>
       <c r="Q1" t="s">
-        <v>69</v>
+        <v>15</v>
       </c>
       <c r="R1" t="s">
-        <v>70</v>
+        <v>16</v>
       </c>
       <c r="S1" t="s">
-        <v>71</v>
+        <v>17</v>
       </c>
       <c r="T1" t="s">
-        <v>72</v>
+        <v>18</v>
       </c>
       <c r="U1" t="s">
-        <v>73</v>
+        <v>19</v>
       </c>
       <c r="V1" t="s">
-        <v>74</v>
+        <v>20</v>
       </c>
       <c r="W1" t="s">
-        <v>75</v>
+        <v>21</v>
       </c>
       <c r="X1" t="s">
-        <v>76</v>
+        <v>22</v>
       </c>
       <c r="Y1" t="s">
-        <v>77</v>
+        <v>23</v>
       </c>
       <c r="Z1" t="s">
-        <v>78</v>
+        <v>24</v>
       </c>
       <c r="AA1" t="s">
-        <v>79</v>
+        <v>25</v>
       </c>
       <c r="AB1" t="s">
-        <v>80</v>
+        <v>26</v>
       </c>
       <c r="AC1" t="s">
-        <v>81</v>
+        <v>27</v>
       </c>
       <c r="AD1" t="s">
-        <v>82</v>
+        <v>28</v>
       </c>
       <c r="AE1" t="s">
-        <v>83</v>
+        <v>29</v>
       </c>
       <c r="AF1" t="s">
-        <v>84</v>
-      </c>
-      <c r="AG1" t="s">
-        <v>85</v>
-      </c>
-      <c r="AH1" t="s">
-        <v>86</v>
+        <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>286</v>
+        <v>131</v>
       </c>
       <c r="B2">
         <v>10</v>
@@ -12333,25 +11250,19 @@
       <c r="AC2">
         <v>8</v>
       </c>
-      <c r="AD2" t="s">
-        <v>0</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>1</v>
+      <c r="AD2">
+        <v>11.530382156371999</v>
+      </c>
+      <c r="AE2">
+        <v>9.7883908748626691</v>
       </c>
       <c r="AF2">
-        <v>11.530382156371999</v>
-      </c>
-      <c r="AG2">
-        <v>9.7883908748626691</v>
-      </c>
-      <c r="AH2">
         <v>21.318773031234699</v>
       </c>
     </row>
-    <row r="3" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>287</v>
+        <v>132</v>
       </c>
       <c r="B3">
         <v>10</v>
@@ -12438,25 +11349,19 @@
       <c r="AC3">
         <v>10</v>
       </c>
-      <c r="AD3" t="s">
-        <v>2</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>3</v>
+      <c r="AD3">
+        <v>11.4522349834442</v>
+      </c>
+      <c r="AE3">
+        <v>4.0370209217071498</v>
       </c>
       <c r="AF3">
-        <v>11.4522349834442</v>
-      </c>
-      <c r="AG3">
-        <v>4.0370209217071498</v>
-      </c>
-      <c r="AH3">
         <v>15.4892559051513</v>
       </c>
     </row>
-    <row r="4" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>288</v>
+        <v>133</v>
       </c>
       <c r="B4">
         <v>10</v>
@@ -12543,25 +11448,19 @@
       <c r="AC4">
         <v>4</v>
       </c>
-      <c r="AD4" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE4" t="s">
-        <v>5</v>
+      <c r="AD4">
+        <v>12.1135540008544</v>
+      </c>
+      <c r="AE4">
+        <v>6.0623002052307102</v>
       </c>
       <c r="AF4">
-        <v>12.1135540008544</v>
-      </c>
-      <c r="AG4">
-        <v>6.0623002052307102</v>
-      </c>
-      <c r="AH4">
         <v>18.175854206085202</v>
       </c>
     </row>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>289</v>
+        <v>134</v>
       </c>
       <c r="B5">
         <v>10</v>
@@ -12648,25 +11547,19 @@
       <c r="AC5">
         <v>11</v>
       </c>
-      <c r="AD5" t="s">
-        <v>6</v>
-      </c>
-      <c r="AE5" t="s">
-        <v>3</v>
+      <c r="AD5">
+        <v>11.541048049926699</v>
+      </c>
+      <c r="AE5">
+        <v>15.2159028053283</v>
       </c>
       <c r="AF5">
-        <v>11.541048049926699</v>
-      </c>
-      <c r="AG5">
-        <v>15.2159028053283</v>
-      </c>
-      <c r="AH5">
         <v>26.756950855255099</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>290</v>
+        <v>135</v>
       </c>
       <c r="B6">
         <v>10</v>
@@ -12753,25 +11646,19 @@
       <c r="AC6">
         <v>3</v>
       </c>
-      <c r="AD6" t="s">
-        <v>7</v>
-      </c>
-      <c r="AE6" t="s">
-        <v>5</v>
+      <c r="AD6">
+        <v>11.7057838439941</v>
+      </c>
+      <c r="AE6">
+        <v>4.1515369415283203</v>
       </c>
       <c r="AF6">
-        <v>11.7057838439941</v>
-      </c>
-      <c r="AG6">
-        <v>4.1515369415283203</v>
-      </c>
-      <c r="AH6">
         <v>15.857320785522401</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>291</v>
+        <v>136</v>
       </c>
       <c r="B7">
         <v>10</v>
@@ -12858,25 +11745,19 @@
       <c r="AC7">
         <v>7</v>
       </c>
-      <c r="AD7" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE7" t="s">
-        <v>3</v>
+      <c r="AD7">
+        <v>11.972319126129101</v>
+      </c>
+      <c r="AE7">
+        <v>4.8515529632568297</v>
       </c>
       <c r="AF7">
-        <v>11.972319126129101</v>
-      </c>
-      <c r="AG7">
-        <v>4.8515529632568297</v>
-      </c>
-      <c r="AH7">
         <v>16.823872089385901</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>292</v>
+        <v>137</v>
       </c>
       <c r="B8">
         <v>10</v>
@@ -12963,25 +11844,19 @@
       <c r="AC8">
         <v>3</v>
       </c>
-      <c r="AD8" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE8" t="s">
-        <v>3</v>
+      <c r="AD8">
+        <v>13.5317800045013</v>
+      </c>
+      <c r="AE8">
+        <v>4.3714292049407897</v>
       </c>
       <c r="AF8">
-        <v>13.5317800045013</v>
-      </c>
-      <c r="AG8">
-        <v>4.3714292049407897</v>
-      </c>
-      <c r="AH8">
         <v>17.9032092094421</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>293</v>
+        <v>138</v>
       </c>
       <c r="B9">
         <v>10</v>
@@ -13068,25 +11943,19 @@
       <c r="AC9">
         <v>6</v>
       </c>
-      <c r="AD9" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE9" t="s">
-        <v>3</v>
+      <c r="AD9">
+        <v>11.5264971256256</v>
+      </c>
+      <c r="AE9">
+        <v>4.1621809005737296</v>
       </c>
       <c r="AF9">
-        <v>11.5264971256256</v>
-      </c>
-      <c r="AG9">
-        <v>4.1621809005737296</v>
-      </c>
-      <c r="AH9">
         <v>15.6886780261993</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>294</v>
+        <v>139</v>
       </c>
       <c r="B10">
         <v>10</v>
@@ -13173,25 +12042,19 @@
       <c r="AC10">
         <v>8</v>
       </c>
-      <c r="AD10" t="s">
-        <v>11</v>
-      </c>
-      <c r="AE10" t="s">
-        <v>12</v>
+      <c r="AD10">
+        <v>10.630830049514699</v>
+      </c>
+      <c r="AE10">
+        <v>12.5811069011688</v>
       </c>
       <c r="AF10">
-        <v>10.630830049514699</v>
-      </c>
-      <c r="AG10">
-        <v>12.5811069011688</v>
-      </c>
-      <c r="AH10">
         <v>23.211936950683501</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>295</v>
+        <v>140</v>
       </c>
       <c r="B11">
         <v>10</v>
@@ -13278,25 +12141,19 @@
       <c r="AC11">
         <v>12</v>
       </c>
-      <c r="AD11" t="s">
-        <v>13</v>
-      </c>
-      <c r="AE11" t="s">
-        <v>1</v>
+      <c r="AD11">
+        <v>12.001085996627801</v>
+      </c>
+      <c r="AE11">
+        <v>9.3939309120178205</v>
       </c>
       <c r="AF11">
-        <v>12.001085996627801</v>
-      </c>
-      <c r="AG11">
-        <v>9.3939309120178205</v>
-      </c>
-      <c r="AH11">
         <v>21.395016908645601</v>
       </c>
     </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>296</v>
+        <v>141</v>
       </c>
       <c r="B12">
         <v>20</v>
@@ -13383,25 +12240,19 @@
       <c r="AC12">
         <v>7</v>
       </c>
-      <c r="AD12" t="s">
-        <v>14</v>
-      </c>
-      <c r="AE12" t="s">
-        <v>3</v>
+      <c r="AD12">
+        <v>50.414642810821498</v>
+      </c>
+      <c r="AE12">
+        <v>16.8379802703857</v>
       </c>
       <c r="AF12">
-        <v>50.414642810821498</v>
-      </c>
-      <c r="AG12">
-        <v>16.8379802703857</v>
-      </c>
-      <c r="AH12">
         <v>67.252623081207204</v>
       </c>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>297</v>
+        <v>142</v>
       </c>
       <c r="B13">
         <v>20</v>
@@ -13488,25 +12339,19 @@
       <c r="AC13">
         <v>16</v>
       </c>
-      <c r="AD13" t="s">
-        <v>15</v>
-      </c>
-      <c r="AE13" t="s">
-        <v>3</v>
+      <c r="AD13">
+        <v>51.117758274078298</v>
+      </c>
+      <c r="AE13">
+        <v>36.710703849792402</v>
       </c>
       <c r="AF13">
-        <v>51.117758274078298</v>
-      </c>
-      <c r="AG13">
-        <v>36.710703849792402</v>
-      </c>
-      <c r="AH13">
         <v>87.828462123870807</v>
       </c>
     </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>298</v>
+        <v>143</v>
       </c>
       <c r="B14">
         <v>20</v>
@@ -13593,25 +12438,19 @@
       <c r="AC14">
         <v>21</v>
       </c>
-      <c r="AD14" t="s">
-        <v>16</v>
-      </c>
-      <c r="AE14" t="s">
-        <v>3</v>
+      <c r="AD14">
+        <v>45.4097192287445</v>
+      </c>
+      <c r="AE14">
+        <v>16.282850980758599</v>
       </c>
       <c r="AF14">
-        <v>45.4097192287445</v>
-      </c>
-      <c r="AG14">
-        <v>16.282850980758599</v>
-      </c>
-      <c r="AH14">
         <v>61.692570209503103</v>
       </c>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>299</v>
+        <v>144</v>
       </c>
       <c r="B15">
         <v>20</v>
@@ -13698,25 +12537,19 @@
       <c r="AC15">
         <v>12</v>
       </c>
-      <c r="AD15" t="s">
-        <v>17</v>
-      </c>
-      <c r="AE15" t="s">
-        <v>12</v>
+      <c r="AD15">
+        <v>51.192845821380601</v>
+      </c>
+      <c r="AE15">
+        <v>37.4832150936126</v>
       </c>
       <c r="AF15">
-        <v>51.192845821380601</v>
-      </c>
-      <c r="AG15">
-        <v>37.4832150936126</v>
-      </c>
-      <c r="AH15">
         <v>88.676060914993201</v>
       </c>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>300</v>
+        <v>145</v>
       </c>
       <c r="B16">
         <v>20</v>
@@ -13803,25 +12636,19 @@
       <c r="AC16">
         <v>9</v>
       </c>
-      <c r="AD16" t="s">
-        <v>18</v>
-      </c>
-      <c r="AE16" t="s">
-        <v>3</v>
+      <c r="AD16">
+        <v>50.597734928131104</v>
+      </c>
+      <c r="AE16">
+        <v>23.572059154510399</v>
       </c>
       <c r="AF16">
-        <v>50.597734928131104</v>
-      </c>
-      <c r="AG16">
-        <v>23.572059154510399</v>
-      </c>
-      <c r="AH16">
         <v>74.169794082641602</v>
       </c>
     </row>
-    <row r="17" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>301</v>
+        <v>146</v>
       </c>
       <c r="B17">
         <v>20</v>
@@ -13908,25 +12735,19 @@
       <c r="AC17">
         <v>8</v>
       </c>
-      <c r="AD17" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE17" t="s">
-        <v>12</v>
+      <c r="AD17">
+        <v>46.080895900726297</v>
+      </c>
+      <c r="AE17">
+        <v>25.405872821807801</v>
       </c>
       <c r="AF17">
-        <v>46.080895900726297</v>
-      </c>
-      <c r="AG17">
-        <v>25.405872821807801</v>
-      </c>
-      <c r="AH17">
         <v>71.486768722534094</v>
       </c>
     </row>
-    <row r="18" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>302</v>
+        <v>147</v>
       </c>
       <c r="B18">
         <v>20</v>
@@ -14013,25 +12834,19 @@
       <c r="AC18">
         <v>9</v>
       </c>
-      <c r="AD18" t="s">
-        <v>20</v>
-      </c>
-      <c r="AE18" t="s">
-        <v>1</v>
+      <c r="AD18">
+        <v>54.4817311763763</v>
+      </c>
+      <c r="AE18">
+        <v>25.330277919769198</v>
       </c>
       <c r="AF18">
-        <v>54.4817311763763</v>
-      </c>
-      <c r="AG18">
-        <v>25.330277919769198</v>
-      </c>
-      <c r="AH18">
         <v>79.812009096145601</v>
       </c>
     </row>
-    <row r="19" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>303</v>
+        <v>148</v>
       </c>
       <c r="B19">
         <v>20</v>
@@ -14118,25 +12933,19 @@
       <c r="AC19">
         <v>13</v>
       </c>
-      <c r="AD19" t="s">
-        <v>21</v>
-      </c>
-      <c r="AE19" t="s">
-        <v>3</v>
+      <c r="AD19">
+        <v>46.753374099731403</v>
+      </c>
+      <c r="AE19">
+        <v>32.890645027160602</v>
       </c>
       <c r="AF19">
-        <v>46.753374099731403</v>
-      </c>
-      <c r="AG19">
-        <v>32.890645027160602</v>
-      </c>
-      <c r="AH19">
         <v>79.644019126892005</v>
       </c>
     </row>
-    <row r="20" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>304</v>
+        <v>149</v>
       </c>
       <c r="B20">
         <v>20</v>
@@ -14223,25 +13032,19 @@
       <c r="AC20">
         <v>4</v>
       </c>
-      <c r="AD20" t="s">
-        <v>22</v>
-      </c>
-      <c r="AE20" t="s">
-        <v>3</v>
+      <c r="AD20">
+        <v>52.968541860580402</v>
+      </c>
+      <c r="AE20">
+        <v>16.091053962707502</v>
       </c>
       <c r="AF20">
-        <v>52.968541860580402</v>
-      </c>
-      <c r="AG20">
-        <v>16.091053962707502</v>
-      </c>
-      <c r="AH20">
         <v>69.059595823287907</v>
       </c>
     </row>
-    <row r="21" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>305</v>
+        <v>150</v>
       </c>
       <c r="B21">
         <v>20</v>
@@ -14328,25 +13131,19 @@
       <c r="AC21">
         <v>16</v>
       </c>
-      <c r="AD21" t="s">
-        <v>23</v>
-      </c>
-      <c r="AE21" t="s">
-        <v>3</v>
+      <c r="AD21">
+        <v>47.638798713683997</v>
+      </c>
+      <c r="AE21">
+        <v>27.3656389713287</v>
       </c>
       <c r="AF21">
-        <v>47.638798713683997</v>
-      </c>
-      <c r="AG21">
-        <v>27.3656389713287</v>
-      </c>
-      <c r="AH21">
         <v>75.004437685012803</v>
       </c>
     </row>
-    <row r="22" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>306</v>
+        <v>151</v>
       </c>
       <c r="B22">
         <v>30</v>
@@ -14433,25 +13230,19 @@
       <c r="AC22">
         <v>22</v>
       </c>
-      <c r="AD22" t="s">
-        <v>24</v>
-      </c>
-      <c r="AE22" t="s">
-        <v>1</v>
+      <c r="AD22">
+        <v>136.95418095588599</v>
+      </c>
+      <c r="AE22">
+        <v>92.407225131988497</v>
       </c>
       <c r="AF22">
-        <v>136.95418095588599</v>
-      </c>
-      <c r="AG22">
-        <v>92.407225131988497</v>
-      </c>
-      <c r="AH22">
         <v>229.361406087875</v>
       </c>
     </row>
-    <row r="23" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>307</v>
+        <v>152</v>
       </c>
       <c r="B23">
         <v>30</v>
@@ -14538,25 +13329,19 @@
       <c r="AC23">
         <v>13</v>
       </c>
-      <c r="AD23" t="s">
-        <v>25</v>
-      </c>
-      <c r="AE23" t="s">
-        <v>3</v>
+      <c r="AD23">
+        <v>126.695063114166</v>
+      </c>
+      <c r="AE23">
+        <v>31.956833124160699</v>
       </c>
       <c r="AF23">
-        <v>126.695063114166</v>
-      </c>
-      <c r="AG23">
-        <v>31.956833124160699</v>
-      </c>
-      <c r="AH23">
         <v>158.651896238327</v>
       </c>
     </row>
-    <row r="24" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>308</v>
+        <v>153</v>
       </c>
       <c r="B24">
         <v>30</v>
@@ -14643,25 +13428,19 @@
       <c r="AC24">
         <v>11</v>
       </c>
-      <c r="AD24" t="s">
-        <v>26</v>
-      </c>
-      <c r="AE24" t="s">
-        <v>1</v>
+      <c r="AD24">
+        <v>135.830897331237</v>
+      </c>
+      <c r="AE24">
+        <v>43.939877986907902</v>
       </c>
       <c r="AF24">
-        <v>135.830897331237</v>
-      </c>
-      <c r="AG24">
-        <v>43.939877986907902</v>
-      </c>
-      <c r="AH24">
         <v>179.77077531814501</v>
       </c>
     </row>
-    <row r="25" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>309</v>
+        <v>154</v>
       </c>
       <c r="B25">
         <v>30</v>
@@ -14748,25 +13527,19 @@
       <c r="AC25">
         <v>20</v>
       </c>
-      <c r="AD25" t="s">
-        <v>27</v>
-      </c>
-      <c r="AE25" t="s">
-        <v>1</v>
+      <c r="AD25">
+        <v>131.89820909500099</v>
+      </c>
+      <c r="AE25">
+        <v>100.98487091064401</v>
       </c>
       <c r="AF25">
-        <v>131.89820909500099</v>
-      </c>
-      <c r="AG25">
-        <v>100.98487091064401</v>
-      </c>
-      <c r="AH25">
         <v>232.88308000564501</v>
       </c>
     </row>
-    <row r="26" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>310</v>
+        <v>155</v>
       </c>
       <c r="B26">
         <v>30</v>
@@ -14853,25 +13626,19 @@
       <c r="AC26">
         <v>13</v>
       </c>
-      <c r="AD26" t="s">
-        <v>28</v>
-      </c>
-      <c r="AE26" t="s">
-        <v>1</v>
+      <c r="AD26">
+        <v>135.332039117813</v>
+      </c>
+      <c r="AE26">
+        <v>60.508985996246302</v>
       </c>
       <c r="AF26">
-        <v>135.332039117813</v>
-      </c>
-      <c r="AG26">
-        <v>60.508985996246302</v>
-      </c>
-      <c r="AH26">
         <v>195.84102511405899</v>
       </c>
     </row>
-    <row r="27" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>311</v>
+        <v>156</v>
       </c>
       <c r="B27">
         <v>30</v>
@@ -14958,25 +13725,19 @@
       <c r="AC27">
         <v>23</v>
       </c>
-      <c r="AD27" t="s">
-        <v>29</v>
-      </c>
-      <c r="AE27" t="s">
-        <v>3</v>
+      <c r="AD27">
+        <v>130.72081804275501</v>
+      </c>
+      <c r="AE27">
+        <v>76.446866273880005</v>
       </c>
       <c r="AF27">
-        <v>130.72081804275501</v>
-      </c>
-      <c r="AG27">
-        <v>76.446866273880005</v>
-      </c>
-      <c r="AH27">
         <v>207.16768431663499</v>
       </c>
     </row>
-    <row r="28" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>312</v>
+        <v>157</v>
       </c>
       <c r="B28">
         <v>30</v>
@@ -15063,25 +13824,19 @@
       <c r="AC28">
         <v>15</v>
       </c>
-      <c r="AD28" t="s">
-        <v>30</v>
-      </c>
-      <c r="AE28" t="s">
-        <v>3</v>
+      <c r="AD28">
+        <v>137.56320428848201</v>
+      </c>
+      <c r="AE28">
+        <v>33.734876871109002</v>
       </c>
       <c r="AF28">
-        <v>137.56320428848201</v>
-      </c>
-      <c r="AG28">
-        <v>33.734876871109002</v>
-      </c>
-      <c r="AH28">
         <v>171.29808115959099</v>
       </c>
     </row>
-    <row r="29" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>313</v>
+        <v>158</v>
       </c>
       <c r="B29">
         <v>30</v>
@@ -15168,25 +13923,19 @@
       <c r="AC29">
         <v>23</v>
       </c>
-      <c r="AD29" t="s">
-        <v>31</v>
-      </c>
-      <c r="AE29" t="s">
-        <v>1</v>
+      <c r="AD29">
+        <v>139.89398312568599</v>
+      </c>
+      <c r="AE29">
+        <v>121.87328314781099</v>
       </c>
       <c r="AF29">
-        <v>139.89398312568599</v>
-      </c>
-      <c r="AG29">
-        <v>121.87328314781099</v>
-      </c>
-      <c r="AH29">
         <v>261.76726627349802</v>
       </c>
     </row>
-    <row r="30" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>314</v>
+        <v>159</v>
       </c>
       <c r="B30">
         <v>30</v>
@@ -15273,25 +14022,19 @@
       <c r="AC30">
         <v>16</v>
       </c>
-      <c r="AD30" t="s">
-        <v>32</v>
-      </c>
-      <c r="AE30" t="s">
-        <v>1</v>
+      <c r="AD30">
+        <v>223.26606822013801</v>
+      </c>
+      <c r="AE30">
+        <v>82.421515941619802</v>
       </c>
       <c r="AF30">
-        <v>223.26606822013801</v>
-      </c>
-      <c r="AG30">
-        <v>82.421515941619802</v>
-      </c>
-      <c r="AH30">
         <v>305.68758416175802</v>
       </c>
     </row>
-    <row r="31" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>315</v>
+        <v>160</v>
       </c>
       <c r="B31">
         <v>30</v>
@@ -15378,25 +14121,19 @@
       <c r="AC31">
         <v>21</v>
       </c>
-      <c r="AD31" t="s">
-        <v>33</v>
-      </c>
-      <c r="AE31" t="s">
-        <v>3</v>
+      <c r="AD31">
+        <v>148.55995702743499</v>
+      </c>
+      <c r="AE31">
+        <v>120.55933189392</v>
       </c>
       <c r="AF31">
-        <v>148.55995702743499</v>
-      </c>
-      <c r="AG31">
-        <v>120.55933189392</v>
-      </c>
-      <c r="AH31">
         <v>269.11928892135597</v>
       </c>
     </row>
-    <row r="32" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>316</v>
+        <v>161</v>
       </c>
       <c r="B32">
         <v>40</v>
@@ -15483,25 +14220,19 @@
       <c r="AC32">
         <v>23</v>
       </c>
-      <c r="AD32" t="s">
-        <v>34</v>
-      </c>
-      <c r="AE32" t="s">
-        <v>12</v>
+      <c r="AD32">
+        <v>387.48169875144902</v>
+      </c>
+      <c r="AE32">
+        <v>125.17034411430301</v>
       </c>
       <c r="AF32">
-        <v>387.48169875144902</v>
-      </c>
-      <c r="AG32">
-        <v>125.17034411430301</v>
-      </c>
-      <c r="AH32">
         <v>512.65204286575295</v>
       </c>
     </row>
-    <row r="33" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>317</v>
+        <v>162</v>
       </c>
       <c r="B33">
         <v>40</v>
@@ -15588,25 +14319,19 @@
       <c r="AC33">
         <v>23</v>
       </c>
-      <c r="AD33" t="s">
-        <v>35</v>
-      </c>
-      <c r="AE33" t="s">
-        <v>3</v>
+      <c r="AD33">
+        <v>383.48293113708399</v>
+      </c>
+      <c r="AE33">
+        <v>59.670883655548003</v>
       </c>
       <c r="AF33">
-        <v>383.48293113708399</v>
-      </c>
-      <c r="AG33">
-        <v>59.670883655548003</v>
-      </c>
-      <c r="AH33">
         <v>443.153814792633</v>
       </c>
     </row>
-    <row r="34" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>318</v>
+        <v>163</v>
       </c>
       <c r="B34">
         <v>40</v>
@@ -15693,25 +14418,19 @@
       <c r="AC34">
         <v>21</v>
       </c>
-      <c r="AD34" t="s">
-        <v>36</v>
-      </c>
-      <c r="AE34" t="s">
-        <v>3</v>
+      <c r="AD34">
+        <v>315.89736890792801</v>
+      </c>
+      <c r="AE34">
+        <v>159.18544578552201</v>
       </c>
       <c r="AF34">
-        <v>315.89736890792801</v>
-      </c>
-      <c r="AG34">
-        <v>159.18544578552201</v>
-      </c>
-      <c r="AH34">
         <v>475.08281469345002</v>
       </c>
     </row>
-    <row r="35" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>319</v>
+        <v>164</v>
       </c>
       <c r="B35">
         <v>40</v>
@@ -15798,25 +14517,19 @@
       <c r="AC35">
         <v>18</v>
       </c>
-      <c r="AD35" t="s">
-        <v>37</v>
-      </c>
-      <c r="AE35" t="s">
-        <v>3</v>
+      <c r="AD35">
+        <v>416.40254878997803</v>
+      </c>
+      <c r="AE35">
+        <v>80.891351222991901</v>
       </c>
       <c r="AF35">
-        <v>416.40254878997803</v>
-      </c>
-      <c r="AG35">
-        <v>80.891351222991901</v>
-      </c>
-      <c r="AH35">
         <v>497.293900012969</v>
       </c>
     </row>
-    <row r="36" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>320</v>
+        <v>165</v>
       </c>
       <c r="B36">
         <v>40</v>
@@ -15903,25 +14616,19 @@
       <c r="AC36">
         <v>25</v>
       </c>
-      <c r="AD36" t="s">
-        <v>38</v>
-      </c>
-      <c r="AE36" t="s">
-        <v>1</v>
+      <c r="AD36">
+        <v>377.93477916717501</v>
+      </c>
+      <c r="AE36">
+        <v>198.11619591712901</v>
       </c>
       <c r="AF36">
-        <v>377.93477916717501</v>
-      </c>
-      <c r="AG36">
-        <v>198.11619591712901</v>
-      </c>
-      <c r="AH36">
         <v>576.05097508430401</v>
       </c>
     </row>
-    <row r="37" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>321</v>
+        <v>166</v>
       </c>
       <c r="B37">
         <v>40</v>
@@ -16008,25 +14715,19 @@
       <c r="AC37">
         <v>21</v>
       </c>
-      <c r="AD37" t="s">
-        <v>39</v>
-      </c>
-      <c r="AE37" t="s">
-        <v>3</v>
+      <c r="AD37">
+        <v>380.05554103851301</v>
+      </c>
+      <c r="AE37">
+        <v>112.59932804107601</v>
       </c>
       <c r="AF37">
-        <v>380.05554103851301</v>
-      </c>
-      <c r="AG37">
-        <v>112.59932804107601</v>
-      </c>
-      <c r="AH37">
         <v>492.65486907958899</v>
       </c>
     </row>
-    <row r="38" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>322</v>
+        <v>167</v>
       </c>
       <c r="B38">
         <v>40</v>
@@ -16113,25 +14814,19 @@
       <c r="AC38">
         <v>26</v>
       </c>
-      <c r="AD38" t="s">
-        <v>40</v>
-      </c>
-      <c r="AE38" t="s">
-        <v>1</v>
+      <c r="AD38">
+        <v>422.03332877159102</v>
+      </c>
+      <c r="AE38">
+        <v>148.075204133987</v>
       </c>
       <c r="AF38">
-        <v>422.03332877159102</v>
-      </c>
-      <c r="AG38">
-        <v>148.075204133987</v>
-      </c>
-      <c r="AH38">
         <v>570.10853290557804</v>
       </c>
     </row>
-    <row r="39" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>323</v>
+        <v>168</v>
       </c>
       <c r="B39">
         <v>40</v>
@@ -16218,25 +14913,19 @@
       <c r="AC39">
         <v>29</v>
       </c>
-      <c r="AD39" t="s">
-        <v>41</v>
-      </c>
-      <c r="AE39" t="s">
-        <v>3</v>
+      <c r="AD39">
+        <v>325.324321746826</v>
+      </c>
+      <c r="AE39">
+        <v>124.367469787597</v>
       </c>
       <c r="AF39">
-        <v>325.324321746826</v>
-      </c>
-      <c r="AG39">
-        <v>124.367469787597</v>
-      </c>
-      <c r="AH39">
         <v>449.69179153442298</v>
       </c>
     </row>
-    <row r="40" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>324</v>
+        <v>169</v>
       </c>
       <c r="B40">
         <v>40</v>
@@ -16323,25 +15012,19 @@
       <c r="AC40">
         <v>17</v>
       </c>
-      <c r="AD40" t="s">
-        <v>42</v>
-      </c>
-      <c r="AE40" t="s">
-        <v>3</v>
+      <c r="AD40">
+        <v>335.89109611511202</v>
+      </c>
+      <c r="AE40">
+        <v>106.524478912353</v>
       </c>
       <c r="AF40">
-        <v>335.89109611511202</v>
-      </c>
-      <c r="AG40">
-        <v>106.524478912353</v>
-      </c>
-      <c r="AH40">
         <v>442.41557502746502</v>
       </c>
     </row>
-    <row r="41" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>325</v>
+        <v>170</v>
       </c>
       <c r="B41">
         <v>40</v>
@@ -16428,25 +15111,19 @@
       <c r="AC41">
         <v>20</v>
       </c>
-      <c r="AD41" t="s">
-        <v>43</v>
-      </c>
-      <c r="AE41" t="s">
-        <v>1</v>
+      <c r="AD41">
+        <v>275.21182990074101</v>
+      </c>
+      <c r="AE41">
+        <v>84.089141130447302</v>
       </c>
       <c r="AF41">
-        <v>275.21182990074101</v>
-      </c>
-      <c r="AG41">
-        <v>84.089141130447302</v>
-      </c>
-      <c r="AH41">
         <v>359.300971031188</v>
       </c>
     </row>
-    <row r="42" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>326</v>
+        <v>171</v>
       </c>
       <c r="B42">
         <v>50</v>
@@ -16533,25 +15210,19 @@
       <c r="AC42">
         <v>20</v>
       </c>
-      <c r="AD42" t="s">
-        <v>44</v>
-      </c>
-      <c r="AE42" t="s">
-        <v>1</v>
+      <c r="AD42">
+        <v>920.86828923225403</v>
+      </c>
+      <c r="AE42">
+        <v>125.94367909431401</v>
       </c>
       <c r="AF42">
-        <v>920.86828923225403</v>
-      </c>
-      <c r="AG42">
-        <v>125.94367909431401</v>
-      </c>
-      <c r="AH42">
         <v>1046.81196832656</v>
       </c>
     </row>
-    <row r="43" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>327</v>
+        <v>172</v>
       </c>
       <c r="B43">
         <v>50</v>
@@ -16638,25 +15309,19 @@
       <c r="AC43">
         <v>18</v>
       </c>
-      <c r="AD43" t="s">
-        <v>45</v>
-      </c>
-      <c r="AE43" t="s">
-        <v>3</v>
+      <c r="AD43">
+        <v>1526.5308821201299</v>
+      </c>
+      <c r="AE43">
+        <v>195.112702369689</v>
       </c>
       <c r="AF43">
-        <v>1526.5308821201299</v>
-      </c>
-      <c r="AG43">
-        <v>195.112702369689</v>
-      </c>
-      <c r="AH43">
         <v>1721.6435844898199</v>
       </c>
     </row>
-    <row r="44" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>328</v>
+        <v>173</v>
       </c>
       <c r="B44">
         <v>50</v>
@@ -16743,25 +15408,19 @@
       <c r="AC44">
         <v>37</v>
       </c>
-      <c r="AD44" t="s">
-        <v>46</v>
-      </c>
-      <c r="AE44" t="s">
-        <v>1</v>
+      <c r="AD44">
+        <v>953.887783050537</v>
+      </c>
+      <c r="AE44">
+        <v>225.667033910751</v>
       </c>
       <c r="AF44">
-        <v>953.887783050537</v>
-      </c>
-      <c r="AG44">
-        <v>225.667033910751</v>
-      </c>
-      <c r="AH44">
         <v>1179.55481696128</v>
       </c>
     </row>
-    <row r="45" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>329</v>
+        <v>174</v>
       </c>
       <c r="B45">
         <v>50</v>
@@ -16848,25 +15507,19 @@
       <c r="AC45">
         <v>33</v>
       </c>
-      <c r="AD45" t="s">
-        <v>47</v>
-      </c>
-      <c r="AE45" t="s">
-        <v>1</v>
+      <c r="AD45">
+        <v>1031.6846191883001</v>
+      </c>
+      <c r="AE45">
+        <v>232.23698401451099</v>
       </c>
       <c r="AF45">
-        <v>1031.6846191883001</v>
-      </c>
-      <c r="AG45">
-        <v>232.23698401451099</v>
-      </c>
-      <c r="AH45">
         <v>1263.92160320281</v>
       </c>
     </row>
-    <row r="46" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>330</v>
+        <v>175</v>
       </c>
       <c r="B46">
         <v>50</v>
@@ -16953,25 +15606,19 @@
       <c r="AC46">
         <v>40</v>
       </c>
-      <c r="AD46" t="s">
-        <v>48</v>
-      </c>
-      <c r="AE46" t="s">
-        <v>3</v>
+      <c r="AD46">
+        <v>1404.5709979534099</v>
+      </c>
+      <c r="AE46">
+        <v>511.645045995712</v>
       </c>
       <c r="AF46">
-        <v>1404.5709979534099</v>
-      </c>
-      <c r="AG46">
-        <v>511.645045995712</v>
-      </c>
-      <c r="AH46">
         <v>1916.2160439491199</v>
       </c>
     </row>
-    <row r="47" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>331</v>
+        <v>176</v>
       </c>
       <c r="B47">
         <v>50</v>
@@ -17058,25 +15705,19 @@
       <c r="AC47">
         <v>25</v>
       </c>
-      <c r="AD47" t="s">
-        <v>49</v>
-      </c>
-      <c r="AE47" t="s">
-        <v>3</v>
+      <c r="AD47">
+        <v>1421.42409586906</v>
+      </c>
+      <c r="AE47">
+        <v>157.245306968688</v>
       </c>
       <c r="AF47">
-        <v>1421.42409586906</v>
-      </c>
-      <c r="AG47">
-        <v>157.245306968688</v>
-      </c>
-      <c r="AH47">
         <v>1578.6694028377501</v>
       </c>
     </row>
-    <row r="48" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>332</v>
+        <v>177</v>
       </c>
       <c r="B48">
         <v>50</v>
@@ -17163,25 +15804,19 @@
       <c r="AC48">
         <v>36</v>
       </c>
-      <c r="AD48" t="s">
-        <v>50</v>
-      </c>
-      <c r="AE48" t="s">
-        <v>1</v>
+      <c r="AD48">
+        <v>1027.10095500946</v>
+      </c>
+      <c r="AE48">
+        <v>187.06384015083299</v>
       </c>
       <c r="AF48">
-        <v>1027.10095500946</v>
-      </c>
-      <c r="AG48">
-        <v>187.06384015083299</v>
-      </c>
-      <c r="AH48">
         <v>1214.1647951602899</v>
       </c>
     </row>
-    <row r="49" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>333</v>
+        <v>178</v>
       </c>
       <c r="B49">
         <v>50</v>
@@ -17268,25 +15903,19 @@
       <c r="AC49">
         <v>34</v>
       </c>
-      <c r="AD49" t="s">
-        <v>51</v>
-      </c>
-      <c r="AE49" t="s">
-        <v>1</v>
+      <c r="AD49">
+        <v>1059.1911718845299</v>
+      </c>
+      <c r="AE49">
+        <v>214.019200801849</v>
       </c>
       <c r="AF49">
-        <v>1059.1911718845299</v>
-      </c>
-      <c r="AG49">
-        <v>214.019200801849</v>
-      </c>
-      <c r="AH49">
         <v>1273.21037268638</v>
       </c>
     </row>
-    <row r="50" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>334</v>
+        <v>179</v>
       </c>
       <c r="B50">
         <v>50</v>
@@ -17373,25 +16002,19 @@
       <c r="AC50">
         <v>35</v>
       </c>
-      <c r="AD50" t="s">
-        <v>52</v>
-      </c>
-      <c r="AE50" t="s">
-        <v>3</v>
+      <c r="AD50">
+        <v>1039.9100790023799</v>
+      </c>
+      <c r="AE50">
+        <v>178.166967153549</v>
       </c>
       <c r="AF50">
-        <v>1039.9100790023799</v>
-      </c>
-      <c r="AG50">
-        <v>178.166967153549</v>
-      </c>
-      <c r="AH50">
         <v>1218.07704615592</v>
       </c>
     </row>
-    <row r="51" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>335</v>
+        <v>180</v>
       </c>
       <c r="B51">
         <v>50</v>
@@ -17478,19 +16101,13 @@
       <c r="AC51">
         <v>29</v>
       </c>
-      <c r="AD51" t="s">
-        <v>53</v>
-      </c>
-      <c r="AE51" t="s">
-        <v>3</v>
+      <c r="AD51">
+        <v>868.00721979141201</v>
+      </c>
+      <c r="AE51">
+        <v>171.90956711769101</v>
       </c>
       <c r="AF51">
-        <v>868.00721979141201</v>
-      </c>
-      <c r="AG51">
-        <v>171.90956711769101</v>
-      </c>
-      <c r="AH51">
         <v>1039.9167869091</v>
       </c>
     </row>
